--- a/report.xlsx
+++ b/report.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Requirements'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Elements'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TestCases'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TestCases'!$A$1:$J$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Summary'!$A$1:$F$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'GenerationLog'!$A$1:$F$1</definedName>
   </definedNames>
@@ -479,18 +479,18 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>При вызове подкомпонента HAL_CRC_MspInit компонент INIT должен выполнить следующее: если значение поля Instance структуры crcHandle равно константе CRC, необходимо включить тактирование модуля CRC вызовом макроса __HAL_RCC_CRC_CLK_ENABLE() без аргументов</t>
+          <t>При вызове SetLevel с целочисленным аргументом value в диапазоне от 0 до 100 включительно компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK. Если value меньше 0 или больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения.</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\Пользователь\PycharmProjects\diplom\examples\requirements.docx</t>
+          <t>C:\Users\Пользователь\PycharmProjects\diplom\examples\demo_suite\small_sets\DEMO_RANGE_001\requirements.txt</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -557,12 +557,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E001</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -572,12 +572,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>При вызове подкомпонента HAL_CRC_MspInit</t>
+          <t>При вызове SetLevel с целочисленным аргументом value в диапазоне от 0 до 100 включительно</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>При вызове подкомпонента HAL_CRC_MspInit</t>
+          <t>При вызове SetLevel с целочисленным аргументом value в диапазоне от 0 до 100 включительно</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -589,27 +589,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E002</t>
+          <t>DEMO_RANGE_001::E002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>условие</t>
+          <t>действие</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>если значение поля Instance структуры crcHandle равно константе CRC</t>
+          <t>компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>если значение поля Instance структуры crcHandle равно константе CRC</t>
+          <t>компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -621,27 +621,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E003</t>
+          <t>DEMO_RANGE_001::E003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>действие</t>
+          <t>ограничение</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>необходимо включить тактирование модуля CRC вызовом макроса __HAL_RCC_CRC_CLK_ENABLE()</t>
+          <t>Если value меньше 0 или больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>необходимо включить тактирование модуля CRC вызовом макроса __HAL_RCC_CRC_CLK_ENABLE()</t>
+          <t>Если value меньше 0 или больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -653,27 +653,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E004</t>
+          <t>DEMO_RANGE_001::E004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ограничение</t>
+          <t>диапазон</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>без аргументов</t>
+          <t>в диапазоне от 0 до 100 включительно</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>без аргументов</t>
+          <t>в диапазоне от 0 до 100 включительно</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -764,37 +764,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC_CRC_001</t>
+          <t>TC_RANGE_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Включение тактирования CRC</t>
+          <t>Допустимый value=0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>["crcHandle.Instance равно CRC"]</t>
+          <t>["currentLevel = 25"]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>{"crcHandle.Instance": "CRC"}</t>
+          <t>{"value": "0"}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>["Вызвать HAL_CRC_MspInit", "Зафиксировать вызовы макросов"]</t>
+          <t>["Вызвать SetLevel(0)", "Проверить currentLevel и возвращаемый статус"]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Вызван __HAL_RCC_CRC_CLK_ENABLE() без аргументов; тактирование CRC включено</t>
+          <t>currentLevel = 0; возвращён STATUS_OK</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -813,8 +813,268 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Допустимый value=50</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>["currentLevel = 25"]</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>{"value": "50"}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать SetLevel(50)", "Проверить currentLevel и возвращаемый статус"]</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>currentLevel = 50; возвращён STATUS_OK</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Допустимый value=100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>["currentLevel = 25"]</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{"value": "100"}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать SetLevel(100)", "Проверить currentLevel и возвращаемый статус"]</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>currentLevel = 100; возвращён STATUS_OK</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Недопустимый value=-1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>["currentLevel = 25"]</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>{"value": "-1"}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать SetLevel(-1)", "Проверить статус и сохранность currentLevel"]</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Возвращён STATUS_RANGE_ERROR; currentLevel = 25</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Недопустимый value=101</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>["currentLevel = 25"]</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>{"value": "101"}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"]</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Возвращён STATUS_RANGE_ERROR; currentLevel = 25</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_BAD</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Ошибочный статус для value=101</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>["currentLevel = 25"]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>{"value": "101"}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать SetLevel(101)"]</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Возвращён STATUS_OK; currentLevel = 101</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -825,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -857,122 +1117,222 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>TC_CRC_001</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
+          <t>TC_RANGE_01</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TC_RANGE_02</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TC_RANGE_03</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TC_RANGE_04</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TC_RANGE_05</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TC_RANGE_BAD</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E001</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>При вызове подкомпонента HAL_CRC_MspInit</t>
+          <t>При вызове SetLevel с целочисленным аргументом value в диапазоне от 0 до 100 включительно</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>покрыт</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E002</t>
+          <t>DEMO_RANGE_001::E002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>если значение поля Instance структуры crcHandle равно константе CRC</t>
+          <t>компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>покрыт</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E003</t>
+          <t>DEMO_RANGE_001::E003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>необходимо включить тактирование модуля CRC вызовом макроса __HAL_RCC_CRC_CLK_ENABLE()</t>
+          <t>Если value меньше 0 или больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>покрыт</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E004</t>
+          <t>DEMO_RANGE_001::E004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>без аргументов</t>
+          <t>в диапазоне от 0 до 100 включительно</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>покрыт</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -1050,186 +1410,923 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E001</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TC_CRC_001</t>
+          <t>TC_RANGE_01</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>покрыт</t>
+          <t>требует проверки</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_CRC_001 покрывает требование SDD_MVA_INIT_F_00040, так как он проверяет вызов HAL_CRC_MspInit при условии, что crcHandle.Instance равно CRC, и ожидает вызова __HAL_RCC_CRC_CLK_ENABLE() без аргументов.
-Точные совпадения: HAL_CRC_MspInit
-Отсутствующие токены: нет
-Цитаты теста: {"preconditions": ["crcHandle.Instance равно CRC"], "steps": ["Вызвать HAL_CRC_MspInit", "Зафиксировать вызовы макросов"], "expected_result": ["Вызван __HAL_RCC_CRC_CLK_ENABLE() без аргументов; тактирование CRC включено"]}</t>
+          <t>Тест не покрывает все значения диапазона от 0 до 100 включительно и не проверяет значение value больше 100.
+Точные совпадения: 0, SetLevel
+Отсутствующие токены: 100, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(0)"], "expected_result": ["currentLevel = 0; возвращён STATUS_OK"]}</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F9" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>принят</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>покрыт</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E002</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>TC_CRC_001</t>
+          <t>TC_RANGE_02</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>покрыт</t>
+          <t>требует проверки</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_CRC_001 содержит все необходимые условия и действия, описанные в требовании SDD_MVA_INIT_F_00040. Тест фиксирует вызовы макросов и проверяет, что __HAL_RCC_CRC_CLK_ENABLE() вызывается без аргументов при условии, что crcHandle.Instance равно CRC.
-Точные совпадения: CRC, Instance, crcHandle
-Отсутствующие токены: нет
-Цитаты теста: {"preconditions": ["crcHandle.Instance равно CRC"], "steps": ["Вызвать HAL_CRC_MspInit", "Зафиксировать вызовы макросов"], "expected_result": ["Вызван __HAL_RCC_CRC_CLK_ENABLE() без аргументов; тактирование CRC включено"]}</t>
+          <t>Тест TC_RANGE_02 проверяет поведение компонента при вызове SetLevel с допустимым значением value=50, что соответствует условию элемента DEMO_RANGE_001::E001. В тесте указаны предусловия, шаги и ожидаемый результат, которые полностью соответствуют требованию.
+Точные совпадения: SetLevel
+Отсутствующие токены: 0, 100, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(50)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 50; возвращён STATUS_OK"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 0, 100, value</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>принят</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>покрыт</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E003</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TC_CRC_001</t>
+          <t>TC_RANGE_03</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>покрыт</t>
+          <t>требует проверки</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_CRC_001 соответствует требованию SDD_MVA_INIT_F_00040, так как в предусловиях указано, что crcHandle.Instance равно CRC, что соответствует условию из требования. В шагах теста вызывается HAL_CRC_MspInit, а в ожидаемом результате указан вызов __HAL_RCC_CRC_CLK_ENABLE() без аргументов, что также соответствует требованию.
-Точные совпадения: CRC, __HAL_RCC_CRC_CLK_ENABLE
-Отсутствующие токены: нет
-Цитаты теста: {"preconditions": ["crcHandle.Instance равно CRC"], "steps": ["Вызвать HAL_CRC_MspInit", "Зафиксировать вызовы макросов"], "expected_result": ["Вызван __HAL_RCC_CRC_CLK_ENABLE() без аргументов; тактирование CRC включено"]}</t>
+          <t>Тест TC_RANGE_03 проверяет поведение компонента при вызове SetLevel с допустимым значением value = 100. В соответствии с требованием, компонент должен сохранить значение в поле currentLevel и вернуть STATUS_OK. Тест выполняет эти действия и проверяет ожидаемый результат.
+Точные совпадения: 100, SetLevel
+Отсутствующие токены: 0, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(100)"], "expected_result": ["currentLevel = 100; возвращён STATUS_OK"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 0, value</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>принят</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>покрыт</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040::E004</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TC_CRC_001</t>
+          <t>TC_RANGE_04</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>покрыт</t>
+          <t>не покрыт</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_CRC_001 соответствует требованию SDD_MVA_INIT_F_00040, так как он проверяет вызов __HAL_RCC_CRC_CLK_ENABLE() без аргументов при условии, что crcHandle.Instance равно CRC.
+          <t>Тест не покрывает все значения диапазона от 0 до 100 включительно и не проверяет значение value = 100.
+Точные совпадения: SetLevel
+Отсутствующие токены: 0, 100, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(-1)"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E001</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_05</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Тест не покрывает диапазон значений от 0 до 100 включительно, а также не проверяет значение value=101.
+Точные совпадения: SetLevel
+Отсутствующие токены: 0, 100, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E001</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_BAD</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Тест не покрывает диапазон значений от 0 до 100 включительно, а также не проверяет значение value=101.
+Точные совпадения: SetLevel
+Отсутствующие токены: 0, 100, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)"], "expected_result": ["Возвращён STATUS_OK; currentLevel = 101"]}</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E002</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_01</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_01 проверяет действие, описанное в элементе DEMO_RANGE_001::E002, при допустимом значении value (0). Тест содержит предусловие, шаги и ожидаемый результат, которые полностью соответствуют описанию элемента.
+Точные совпадения: STATUS_OK, currentLevel
+Отсутствующие токены: value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(0)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 0; возвращён STATUS_OK"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: value</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E002</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_02</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_02 проверяет действие E002, подтверждая, что при вызове SetLevel с допустимым значением value=50 компонент сохраняет это значение в поле currentLevel и возвращает STATUS_OK. В предусловиях указано, что currentLevel = 25, что соответствует условию требования. В шагах теста указано, что вызывается SetLevel(50), а в ожидаемом результате указано, что currentLevel = 50 и возвращён STATUS_OK, что соответствует требованию.
+Точные совпадения: STATUS_OK, currentLevel
+Отсутствующие токены: value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(50)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 50; возвращён STATUS_OK"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: value</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E002</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_03</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_03 проверяет действие, описанное в элементе DEMO_RANGE_001::E002, при допустимом значении value = 100. В предусловиях указано, что currentLevel = 25, что соответствует условию диапазона от 0 до 100 включительно. В шагах теста вызывается SetLevel(100), а в ожидаемом результате проверяется, что currentLevel = 100 и возвращён STATUS_OK, что соответствует описанию элемента.
+Точные совпадения: STATUS_OK, currentLevel
+Отсутствующие токены: value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(100)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 100; возвращён STATUS_OK"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: value</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E002</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_04</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_04 проверяет возврат STATUS_RANGE_ERROR при недопустимом значении, но не проверяет сохранение значения currentLevel и возврат STATUS_OK для допустимого значения.
+Точные совпадения: currentLevel
+Отсутствующие токены: STATUS_OK, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(-1)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E002</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_05</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_05 проверяет возврат STATUS_RANGE_ERROR при value=101, но не проверяет сохранение значения currentLevel и возврат STATUS_OK при допустимом value.
+Точные совпадения: currentLevel
+Отсутствующие токены: STATUS_OK, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E002</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_BAD</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Тест не проверяет возвращение STATUS_RANGE_ERROR и оставление currentLevel без изменения для значения value, которое меньше 0 или больше 100.
+Точные совпадения: STATUS_OK, currentLevel
+Отсутствующие токены: value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)"], "expected_result": ["Возвращён STATUS_OK; currentLevel = 101"]}</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E003</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_01</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_01 проверяет только значение value = 0, которое находится в допустимом диапазоне от 0 до 100 включительно. Тест не покрывает значения, которые должны вызвать ошибку STATUS_RANGE_ERROR, такие как value &lt; 0 и value &gt; 100.
+Точные совпадения: 0, currentLevel
+Отсутствующие токены: 100, STATUS_RANGE_ERROR, value
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E003</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_02</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_02 проверяет только значение value = 50, которое находится в допустимом диапазоне от 0 до 100 включительно. Тест не покрывает случаи, когда value меньше 0 или больше 100, которые описаны в элементе DEMO_RANGE_001::E003.
+Точные совпадения: currentLevel
+Отсутствующие токены: 0, 100, STATUS_RANGE_ERROR, value
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E003</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_03</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_03 проверяет только значение value = 100 и не покрывает случаи, когда value меньше 0 или больше 100.
+Точные совпадения: 100, currentLevel
+Отсутствующие токены: 0, STATUS_RANGE_ERROR, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(100)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 100; возвращён STATUS_OK"]}</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E003</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_04</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_04 проверяет ветвь, где value меньше 0. В тесте указано, что статус должен быть STATUS_RANGE_ERROR и currentLevel должен остаться без изменения. Это соответствует условию элемента E003, где указано, что если value меньше 0, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения.
+Точные совпадения: STATUS_RANGE_ERROR, currentLevel
+Отсутствующие токены: 0, 100, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(-1)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 0, 100, value</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E003</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_05</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_05 проверяет ветвь, где value больше 100. В тесте указано, что вызов SetLevel(101) должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения. Это соответствует условию элемента E003, где указано, что если value больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения.
+Точные совпадения: STATUS_RANGE_ERROR, currentLevel
+Отсутствующие токены: 0, 100, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 0, 100, value</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E003</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_BAD</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Тест не покрывает все возможные значения value, которые должны вызывать возврат STATUS_RANGE_ERROR. Также отсутствуют проверки для границ диапазона (0 и 100).
+Точные совпадения: currentLevel
+Отсутствующие токены: 0, 100, STATUS_RANGE_ERROR, value
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)"], "expected_result": ["Возвращён STATUS_OK; currentLevel = 101"]}</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E004</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_01</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_01 проверяет нижнюю границу допустимого диапазона (value = 0), что соответствует условию в требовании. В результате теста currentLevel = 0 и возвращён STATUS_OK, что соответствует ожидаемому результату в требовании.
+Точные совпадения: 0
+Отсутствующие токены: 100
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(0)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 0; возвращён STATUS_OK"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 100</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E004</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_02</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_02 покрывает только значение 50, которое находится в пределах диапазона от 0 до 100. Однако, согласно требованию, необходимо проверить все значения в этом диапазоне. Тест не покрывает граничные значения 0 и 100.
 Точные совпадения: нет
-Отсутствующие токены: нет
-Цитаты теста: {"preconditions": ["crcHandle.Instance равно CRC"], "steps": ["Вызвать HAL_CRC_MspInit", "Зафиксировать вызовы макросов"], "expected_result": ["Вызван __HAL_RCC_CRC_CLK_ENABLE() без аргументов; тактирование CRC включено"]}</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>принят</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>покрыт</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+Отсутствующие токены: 0, 100
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(50)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 50; возвращён STATUS_OK"]}</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E004</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_03</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_03 проверяет значение value = 100, которое находится в пределах диапазона от 0 до 100 включительно. В соответствии с требованием, компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK. Тест выполняет вызов SetLevel(100) и проверяет, что currentLevel = 100 и возвращённый статус STATUS_OK соответствует ожидаемому результату.
+Точные совпадения: 100
+Отсутствующие токены: 0
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(100)"], "expected_result": ["currentLevel = 100; возвращён STATUS_OK"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E004</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_04</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_04 проверяет только значение value = -1, которое находится за пределами допустимого диапазона. Тест не покрывает ни нижнюю, ни верхнюю границу диапазона (0 и 100), что соответствует условию элемента DEMO_RANGE_001::E004.
+Точные совпадения: нет
+Отсутствующие токены: 0, 100
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(-1)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E004</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_05</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_RANGE_05 проверяет значение value=101, которое находится за пределами диапазона от 0 до 100 включительно. Однако, согласно требованию, диапазон включает значения от 0 до 100 включительно. Тест не покрывает ни нижний ни верхний пределы диапазона, поэтому требование не полностью покрыто.
+Точные совпадения: нет
+Отсутствующие токены: 0, 100
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_RANGE_001::E004</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>TC_RANGE_BAD</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Тест не покрывает ни нижний ни верхний пределы диапазона от 0 до 100 включительно. Он проверяет значение, которое находится за пределами этого диапазона (101).
+Точные совпадения: нет
+Отсутствующие токены: 0, 100
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)"], "expected_result": ["Возвращён STATUS_OK; currentLevel = 101"]}</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1297,22 +2394,22 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SDD_MVA_INIT_F_00040</t>
+          <t>DEMO_RANGE_001</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1321,16 +2418,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1451,7 +2548,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>{"SDD_MVA_INIT_F_00040": []}</t>
+          <t>{"DEMO_RANGE_001": []}</t>
         </is>
       </c>
       <c r="C12" s="2" t="n"/>

--- a/report.xlsx
+++ b/report.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GenerationLog" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Requirements'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Elements'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TestCases'!$A$1:$J$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Summary'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Requirements'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Elements'!$A$1:$L$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TestCases'!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Summary'!$A$1:$F$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'GenerationLog'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>C:\Users\Пользователь\PycharmProjects\diplom\examples\demo_suite\small_sets\DEMO_RANGE_001\requirements.txt</t>
+          <t>C:\Users\Пользователь\PycharmProjects\diplom\examples\demo_suite\requirements.docx</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -499,8 +499,123 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>При вызове ReadSample в режиме STANDBY компонент должен вернуть STATUS_NOT_READY и не вызывать StartADC. В режиме ACTIVE компонент должен вызвать StartADC() без аргументов; если ADC_READY равно 1, вызвать ReadADC() без аргументов и вернуть прочитанное значение. Поведение в режиме ACTIVE при ADC_READY, отличном от 1, не определено.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\Пользователь\PycharmProjects\diplom\examples\demo_suite\requirements.docx</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>При вызове RetrySend компонент должен вызывать SendFrame(frame) до получения результата SEND_OK, но не более 3 раз. После SEND_OK повторные вызовы SendFrame запрещены, RetrySend должен вернуть STATUS_OK. Если все 3 вызова завершились SEND_ERROR, RetrySend должен вернуть STATUS_SEND_ERROR.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\Пользователь\PycharmProjects\diplom\examples\demo_suite\requirements.docx</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>При вызове HandleTick, если elapsed_ms больше или равно 10, компонент должен вызвать PollSensor() без аргументов ровно один раз за этот вызов HandleTick. Если elapsed_ms меньше 10, PollSensor вызываться не должен. Правила изменения elapsed_ms данным требованием не задаются.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\Пользователь\PycharmProjects\diplom\examples\demo_suite\requirements.docx</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>При вызове UpdateFlags компонент должен вычислить new_flags по формуле (old_flags &amp; ~0x0F) | (requested_flags &amp; 0x0F). В результате биты вне маски 0x0F должны сохранить значения old_flags, а биты внутри маски должны принять значения requested_flags.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\Пользователь\PycharmProjects\diplom\examples\demo_suite\requirements.docx</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_AMBIG_006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ProcessCommand должен быстро обрабатывать команды и корректно реагировать на некорректные входные данные. Список команд, критерии корректности, допустимое время и ожидаемые ответы в этой спецификации не указаны.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>C:\Users\Пользователь\PycharmProjects\diplom\examples\demo_suite\requirements.docx</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -511,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -520,6 +635,12 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,6 +674,36 @@
           <t>review_status</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>conditions</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>analysis_blocked</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>source_refs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>review_notes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>condition_ids</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>negated_condition_ids</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -567,22 +718,50 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>условие</t>
+          <t>обязательство</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>При вызове SetLevel с целочисленным аргументом value в диапазоне от 0 до 100 включительно</t>
+          <t>Компонент сохраняет переданное значение в поле currentLevel и возвращает статус STATUS_OK.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>При вызове SetLevel с целочисленным аргументом value в диапазоне от 0 до 100 включительно</t>
+          <t>При вызове SetLevel с целочисленным аргументом value в диапазоне от 0 до 100 включительно компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q001", "start": 0, "end": 163, "text": "При вызове SetLevel с целочисленным аргументом value в диапазоне от 0 до 100 включительно компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK."}]</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -599,81 +778,137 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>действие</t>
+          <t>обязательство</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK</t>
+          <t>Компонент возвращает статус STATUS_RANGE_ERROR и не изменяет значение поля currentLevel.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK</t>
+          <t>Если value меньше 0 или больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>["Вызов функции SetLevel с аргументом value, меньшим 0", "Вызов функции SetLevel с аргументом value, большим 100"]</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q002", "start": 164, "end": 282, "text": "Если value меньше 0 или больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения."}]</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E003</t>
+          <t>DEMO_MODE_002::E001</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001</t>
+          <t>DEMO_MODE_002</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ограничение</t>
+          <t>обязательство</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Если value меньше 0 или больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения</t>
+          <t>Компонент возвращает STATUS_NOT_READY и не вызывает StartADC.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Если value меньше 0 или больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения</t>
+          <t>При вызове ReadSample в режиме STANDBY компонент должен вернуть STATUS_NOT_READY и не вызывать StartADC.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>["Вызов ReadSample", "Режим STANDBY"]</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q001", "start": 0, "end": 104, "text": "При вызове ReadSample в режиме STANDBY компонент должен вернуть STATUS_NOT_READY и не вызывать StartADC."}]</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E004</t>
+          <t>DEMO_MODE_002::E002</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001</t>
+          <t>DEMO_MODE_002</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>диапазон</t>
+          <t>обязательство</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>в диапазоне от 0 до 100 включительно</t>
+          <t>Компонент вызывает StartADC() без аргументов.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>в диапазоне от 0 до 100 включительно</t>
+          <t>В режиме ACTIVE компонент должен вызвать StartADC() без аргументов</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -681,9 +916,637 @@
           <t>ожидает проверки</t>
         </is>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>["Вызов ReadSample", "Режим ACTIVE"]</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q002", "start": 105, "end": 171, "text": "В режиме ACTIVE компонент должен вызвать StartADC() без аргументов"}]</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002::E003</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>обязательство</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Компонент вызывает ReadADC() без аргументов и возвращает прочитанное значение.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>если ADC_READY равно 1, вызвать ReadADC() без аргументов и вернуть прочитанное значение.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>["Вызов ReadSample", "Режим ACTIVE", "ADC_READY равно 1"]</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q003", "start": 173, "end": 261, "text": "если ADC_READY равно 1, вызвать ReadADC() без аргументов и вернуть прочитанное значение."}]</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E001</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>обязательство</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Компонент должен вызывать SendFrame(frame)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>При вызове RetrySend компонент должен вызывать SendFrame(frame) до получения результата SEND_OK, но не более 3 раз.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>["При вызове функции RetrySend", "До получения результата SEND_OK"]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q001", "start": 0, "end": 115, "text": "При вызове RetrySend компонент должен вызывать SendFrame(frame) до получения результата SEND_OK, но не более 3 раз."}]</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E002</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>обязательство</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Повторные вызовы SendFrame запрещены</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>После SEND_OK повторные вызовы SendFrame запрещены, RetrySend должен вернуть STATUS_OK.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>["При вызове функции RetrySend", "После получения результата SEND_OK"]</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q002", "start": 116, "end": 203, "text": "После SEND_OK повторные вызовы SendFrame запрещены, RetrySend должен вернуть STATUS_OK."}]</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E003</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>обязательство</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>RetrySend должен вернуть STATUS_OK</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>После SEND_OK повторные вызовы SendFrame запрещены, RetrySend должен вернуть STATUS_OK.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>["При вызове функции RetrySend", "После получения результата SEND_OK"]</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q003", "start": 116, "end": 203, "text": "После SEND_OK повторные вызовы SendFrame запрещены, RetrySend должен вернуть STATUS_OK."}]</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E004</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>обязательство</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>RetrySend должен вернуть STATUS_SEND_ERROR</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Если все 3 вызова завершились SEND_ERROR, RetrySend должен вернуть STATUS_SEND_ERROR.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>["При вызове функции RetrySend", "Если все 3 вызова завершились SEND_ERROR"]</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q004", "start": 204, "end": 289, "text": "Если все 3 вызова завершились SEND_ERROR, RetrySend должен вернуть STATUS_SEND_ERROR."}]</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004::E001</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>обязательство</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Компонент должен вызвать функцию PollSensor() без параметров ровно один раз.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>При вызове HandleTick, если elapsed_ms больше или равно 10, компонент должен вызвать PollSensor() без аргументов ровно один раз за этот вызов HandleTick.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>["Вызов функции HandleTick", "Значение переменной elapsed_ms больше или равно 10"]</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q001", "start": 0, "end": 153, "text": "При вызове HandleTick, если elapsed_ms больше или равно 10, компонент должен вызвать PollSensor() без аргументов ровно один раз за этот вызов HandleTick."}]</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004::E002</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>обязательство</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Компонент не должен вызывать функцию PollSensor().</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Если elapsed_ms меньше 10, PollSensor вызываться не должен.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>["Вызов функции HandleTick", "Значение переменной elapsed_ms меньше 10"]</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q002", "start": 154, "end": 213, "text": "Если elapsed_ms меньше 10, PollSensor вызываться не должен."}]</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E001</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>обязательство</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Компонент вычисляет new_flags используя формулу: (old_flags &amp; ~0x0F) | (requested_flags &amp; 0x0F)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>При вызове UpdateFlags компонент должен вычислить new_flags по формуле (old_flags &amp; ~0x0F) | (requested_flags &amp; 0x0F)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>["При вызове метода UpdateFlags"]</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q001", "start": 0, "end": 117, "text": "При вызове UpdateFlags компонент должен вычислить new_flags по формуле (old_flags &amp; ~0x0F) | (requested_flags &amp; 0x0F)"}]</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E002</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>обязательство</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Биты вне маски 0x0F в new_flags сохраняют значения из old_flags</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>В результате биты вне маски 0x0F должны сохранить значения old_flags</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>["При вызове метода UpdateFlags"]</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q002", "start": 119, "end": 187, "text": "В результате биты вне маски 0x0F должны сохранить значения old_flags"}]</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E003</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>обязательство</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Биты внутри маски 0x0F в new_flags принимают значения из requested_flags</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>а биты внутри маски должны принять значения requested_flags</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>["При вызове метода UpdateFlags"]</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>[{"source_id": "Q003", "start": 189, "end": 248, "text": "а биты внутри маски должны принять значения requested_flags"}]</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:L15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -694,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1073,8 +1936,788 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC_MODE_STANDBY</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>STANDBY без запуска ADC</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>["Режим = STANDBY"]</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>{"mode": "STANDBY"}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>["Очистить журнал вызовов", "Вызвать ReadSample", "Проверить статус и журнал StartADC"]</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Возвращён STATUS_NOT_READY; StartADC не вызван</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC_MODE_ACTIVE</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE с готовым ADC</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>["Режим = ACTIVE", "ADC_READY = 1", "ReadADC возвращает 42"]</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>{"mode": "ACTIVE", "ADC_READY": "1", "sample": "42"}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать ReadSample", "Зафиксировать вызовы StartADC и ReadADC и возвращаемое значение"]</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>StartADC() вызван без аргументов; ReadADC() вызван без аргументов; возвращено 42</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC_MODE_UNSPEC</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Выдуманное поведение при неготовом ADC</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>["Режим = ACTIVE", "ADC_READY = 0"]</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>{"mode": "ACTIVE", "ADC_READY": "0"}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать ReadSample"]</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Возвращён STATUS_TIMEOUT</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FIRST</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>RetrySend: FIRST</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>["frame подготовлен", "Заглушка SendFrame возвращает заданную последовательность"]</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>{"SendFrame_returns": "SEND_OK", "frame": "учебный кадр"}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать RetrySend", "Проверить число вызовов SendFrame(frame) и статус RetrySend"]</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>SendFrame(frame) вызван 1 раз; RetrySend вернул STATUS_OK; дополнительных вызовов нет</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_THIRD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>RetrySend: THIRD</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>["frame подготовлен", "Заглушка SendFrame возвращает заданную последовательность"]</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>{"SendFrame_returns": "SEND_ERROR, SEND_ERROR, SEND_OK", "frame": "учебный кадр"}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать RetrySend", "Проверить число вызовов SendFrame(frame) и статус RetrySend"]</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>SendFrame(frame) вызван 3 раз; RetrySend вернул STATUS_OK; дополнительных вызовов нет</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FAIL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>RetrySend: FAIL</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>["frame подготовлен", "Заглушка SendFrame возвращает заданную последовательность"]</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>{"SendFrame_returns": "SEND_ERROR, SEND_ERROR, SEND_ERROR", "frame": "учебный кадр"}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать RetrySend", "Проверить число вызовов SendFrame(frame) и статус RetrySend"]</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>SendFrame(frame) вызван 3 раз; RetrySend вернул STATUS_SEND_ERROR; дополнительных вызовов нет</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_PARTIAL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Неполная проверка RetrySend</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>["SendFrame всегда возвращает SEND_ERROR"]</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>{"SendFrame_returns": "SEND_ERROR"}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать RetrySend"]</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>RetrySend вернул STATUS_SEND_ERROR</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_BAD</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Противоречивый предел повторов</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>["SendFrame всегда возвращает SEND_ERROR"]</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>{"SendFrame_returns": "SEND_ERROR"}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать RetrySend", "Подсчитать вызовы SendFrame(frame)"]</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>SendFrame(frame) вызван 4 раза; возвращён STATUS_SEND_ERROR</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC_TIME_9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>elapsed_ms=9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>["Журнал PollSensor очищен"]</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>{"elapsed_ms": "9"}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать HandleTick с elapsed_ms=9", "Подсчитать вызовы PollSensor"]</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>PollSensor не вызван</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TC_TIME_10</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>elapsed_ms=10</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>["Журнал PollSensor очищен"]</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>{"elapsed_ms": "10"}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать HandleTick с elapsed_ms=10", "Подсчитать вызовы PollSensor"]</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>PollSensor() вызван без аргументов ровно 1 раз</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC_TIME_11</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>elapsed_ms=11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>["Журнал PollSensor очищен"]</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>{"elapsed_ms": "11"}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать HandleTick с elapsed_ms=11", "Подсчитать вызовы PollSensor"]</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>PollSensor() вызван без аргументов ровно 1 раз</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_GOOD</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Обновление только младших битов</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>["old_flags = 0xA5"]</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>{"old_flags": "0xA5", "requested_flags": "0x3C"}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать UpdateFlags", "Проверить new_flags и отдельно старшие/младшие биты"]</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>new_flags = 0xAC; биты вне 0x0F сохранены от old_flags, биты внутри 0x0F взяты из requested_flags</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_PARTIAL</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Проверены только младшие биты</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>["old_flags = 0xA5"]</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>{"old_flags": "0xA5", "requested_flags": "0x3C"}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать UpdateFlags", "Проверить только new_flags &amp; 0x0F"]</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>new_flags &amp; 0x0F = 0x0C</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Повтор сценария маски с другим названием</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>["old_flags = 0xA5"]</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>{"old_flags": "0xA5", "requested_flags": "0x3C"}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать UpdateFlags", "Проверить new_flags и отдельно старшие/младшие биты"]</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>new_flags = 0xAC; биты вне 0x0F сохранены от old_flags, биты внутри 0x0F взяты из requested_flags</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TC_AMBIG_BAD</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_AMBIG_006</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Выдуманные время и код ошибки</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>["ProcessCommand доступен"]</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>{"command": "???"}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>["Вызвать ProcessCommand с command=???", "Измерить время"]</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>За 5 мс возвращён ERR_INVALID_COMMAND</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>существующий</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J7"/>
+  <autoFilter ref="A1:J22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1085,7 +2728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:X74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1097,6 +2740,21 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="28" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
+    <col width="28" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1145,6 +2803,81 @@
           <t>TC_RANGE_BAD</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TC_MODE_STANDBY</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TC_MODE_ACTIVE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TC_MODE_UNSPEC</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FIRST</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TC_LOOP_THIRD</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FAIL</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TC_LOOP_PARTIAL</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TC_LOOP_BAD</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TC_TIME_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>TC_TIME_10</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TC_TIME_11</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>TC_MASK_GOOD</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>TC_MASK_PARTIAL</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>TC_MASK_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>TC_AMBIG_BAD</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1159,7 +2892,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>При вызове SetLevel с целочисленным аргументом value в диапазоне от 0 до 100 включительно</t>
+          <t>Компонент сохраняет переданное значение в поле currentLevel и возвращает статус STATUS_OK.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1188,6 +2921,81 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>не покрыт</t>
         </is>
@@ -1206,35 +3014,110 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK</t>
+          <t>Компонент возвращает статус STATUS_RANGE_ERROR и не изменяет значение поля currentLevel.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>требует проверки</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>требует проверки</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>не покрыт</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>не покрыт</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>не покрыт</t>
         </is>
@@ -1243,17 +3126,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E003</t>
+          <t>DEMO_MODE_002::E001</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001</t>
+          <t>DEMO_MODE_002</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Если value меньше 0 или больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения</t>
+          <t>Компонент возвращает STATUS_NOT_READY и не вызывает StartADC.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1273,15 +3156,90 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>требует проверки</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>не покрыт</t>
         </is>
@@ -1290,534 +3248,1490 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E004</t>
+          <t>DEMO_MODE_002::E002</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001</t>
+          <t>DEMO_MODE_002</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>в диапазоне от 0 до 100 включительно</t>
+          <t>Компонент вызывает StartADC() без аргументов.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002::E003</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Компонент вызывает ReadADC() без аргументов и возвращает прочитанное значение.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>не покрыт</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>не покрыт</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>не покрыт</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CoverageDecisions</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+          <t>DEMO_LOOP_003::E001</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Компонент должен вызывать SendFrame(frame)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>element_id</t>
+          <t>DEMO_LOOP_003::E002</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>test_case_id</t>
+          <t>DEMO_LOOP_003</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>Повторные вызовы SendFrame запрещены</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>rationale</t>
+          <t>не покрыт</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>не покрыт</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>needs_manual_review</t>
+          <t>не покрыт</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>review_status</t>
+          <t>не покрыт</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>manual_status</t>
+          <t>не покрыт</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>manual_rationale</t>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E001</t>
+          <t>DEMO_LOOP_003::E003</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_01</t>
+          <t>DEMO_LOOP_003</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>RetrySend должен вернуть STATUS_OK</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Тест не покрывает все значения диапазона от 0 до 100 включительно и не проверяет значение value больше 100.
-Точные совпадения: 0, SetLevel
-Отсутствующие токены: 100, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(0)"], "expected_result": ["currentLevel = 0; возвращён STATUS_OK"]}</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>ожидает проверки</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E001</t>
+          <t>DEMO_LOOP_003::E004</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_02</t>
+          <t>DEMO_LOOP_003</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>RetrySend должен вернуть STATUS_SEND_ERROR</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Тест TC_RANGE_02 проверяет поведение компонента при вызове SetLevel с допустимым значением value=50, что соответствует условию элемента DEMO_RANGE_001::E001. В тесте указаны предусловия, шаги и ожидаемый результат, которые полностью соответствуют требованию.
-Точные совпадения: SetLevel
-Отсутствующие токены: 0, 100, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(50)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 50; возвращён STATUS_OK"]}
-Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 0, 100, value</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>ожидает проверки</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E001</t>
+          <t>DEMO_TIME_004::E001</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_03</t>
+          <t>DEMO_TIME_004</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>Компонент должен вызвать функцию PollSensor() без параметров ровно один раз.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Тест TC_RANGE_03 проверяет поведение компонента при вызове SetLevel с допустимым значением value = 100. В соответствии с требованием, компонент должен сохранить значение в поле currentLevel и вернуть STATUS_OK. Тест выполняет эти действия и проверяет ожидаемый результат.
-Точные совпадения: 100, SetLevel
-Отсутствующие токены: 0, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(100)"], "expected_result": ["currentLevel = 100; возвращён STATUS_OK"]}
-Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 0, value</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>ожидает проверки</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E001</t>
+          <t>DEMO_TIME_004::E002</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_04</t>
+          <t>DEMO_TIME_004</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>не покрыт</t>
+          <t>Компонент не должен вызывать функцию PollSensor().</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Тест не покрывает все значения диапазона от 0 до 100 включительно и не проверяет значение value = 100.
-Точные совпадения: SetLevel
-Отсутствующие токены: 0, 100, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(-1)"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F12" s="2" t="b">
-        <v>1</v>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ожидает проверки</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E001</t>
+          <t>DEMO_MASK_005::E001</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_05</t>
+          <t>DEMO_MASK_005</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>не покрыт</t>
+          <t>Компонент вычисляет new_flags используя формулу: (old_flags &amp; ~0x0F) | (requested_flags &amp; 0x0F)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Тест не покрывает диапазон значений от 0 до 100 включительно, а также не проверяет значение value=101.
-Точные совпадения: SetLevel
-Отсутствующие токены: 0, 100, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F13" s="2" t="b">
-        <v>1</v>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ожидает проверки</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E001</t>
+          <t>DEMO_MASK_005::E002</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_BAD</t>
+          <t>DEMO_MASK_005</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>не покрыт</t>
+          <t>Биты вне маски 0x0F в new_flags сохраняют значения из old_flags</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Тест не покрывает диапазон значений от 0 до 100 включительно, а также не проверяет значение value=101.
-Точные совпадения: SetLevel
-Отсутствующие токены: 0, 100, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)"], "expected_result": ["Возвращён STATUS_OK; currentLevel = 101"]}</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F14" s="2" t="b">
-        <v>1</v>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ожидает проверки</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E002</t>
+          <t>DEMO_MASK_005::E003</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_01</t>
+          <t>DEMO_MASK_005</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>Биты внутри маски 0x0F в new_flags принимают значения из requested_flags</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Тест TC_RANGE_01 проверяет действие, описанное в элементе DEMO_RANGE_001::E002, при допустимом значении value (0). Тест содержит предусловие, шаги и ожидаемый результат, которые полностью соответствуют описанию элемента.
-Точные совпадения: STATUS_OK, currentLevel
-Отсутствующие токены: value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(0)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 0; возвращён STATUS_OK"]}
-Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: value</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>ожидает проверки</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>DEMO_RANGE_001::E002</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>TC_RANGE_02</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>требует проверки</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Тест TC_RANGE_02 проверяет действие E002, подтверждая, что при вызове SetLevel с допустимым значением value=50 компонент сохраняет это значение в поле currentLevel и возвращает STATUS_OK. В предусловиях указано, что currentLevel = 25, что соответствует условию требования. В шагах теста указано, что вызывается SetLevel(50), а в ожидаемом результате указано, что currentLevel = 50 и возвращён STATUS_OK, что соответствует требованию.
-Точные совпадения: STATUS_OK, currentLevel
-Отсутствующие токены: value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(50)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 50; возвращён STATUS_OK"]}
-Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: value</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>ожидает проверки</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n"/>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="n"/>
+      <c r="W16" s="2" t="n"/>
+      <c r="X16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E002</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>TC_RANGE_03</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>требует проверки</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Тест TC_RANGE_03 проверяет действие, описанное в элементе DEMO_RANGE_001::E002, при допустимом значении value = 100. В предусловиях указано, что currentLevel = 25, что соответствует условию диапазона от 0 до 100 включительно. В шагах теста вызывается SetLevel(100), а в ожидаемом результате проверяется, что currentLevel = 100 и возвращён STATUS_OK, что соответствует описанию элемента.
-Точные совпадения: STATUS_OK, currentLevel
-Отсутствующие токены: value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(100)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 100; возвращён STATUS_OK"]}
-Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: value</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>ожидает проверки</t>
-        </is>
-      </c>
+          <t>CoverageDecisions</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+      <c r="T17" s="2" t="n"/>
+      <c r="U17" s="2" t="n"/>
+      <c r="V17" s="2" t="n"/>
+      <c r="W17" s="2" t="n"/>
+      <c r="X17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E002</t>
+          <t>element_id</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_04</t>
+          <t>test_case_id</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>не покрыт</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_04 проверяет возврат STATUS_RANGE_ERROR при недопустимом значении, но не проверяет сохранение значения currentLevel и возврат STATUS_OK для допустимого значения.
-Точные совпадения: currentLevel
-Отсутствующие токены: STATUS_OK, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(-1)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F18" s="2" t="b">
-        <v>1</v>
+          <t>rationale</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>needs_manual_review</t>
+        </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ожидает проверки</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>review_status</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>manual_status</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>manual_rationale</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n"/>
+      <c r="T18" s="2" t="n"/>
+      <c r="U18" s="2" t="n"/>
+      <c r="V18" s="2" t="n"/>
+      <c r="W18" s="2" t="n"/>
+      <c r="X18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E002</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_05</t>
+          <t>TC_RANGE_01</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>не покрыт</t>
+          <t>покрыт</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_05 проверяет возврат STATUS_RANGE_ERROR при value=101, но не проверяет сохранение значения currentLevel и возврат STATUS_OK при допустимом value.
-Точные совпадения: currentLevel
-Отсутствующие токены: STATUS_OK, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
+          <t>Тест TC_RANGE_01 полностью покрывает элемент DEMO_RANGE_001::E001. Входной параметр value=0 находится в допустимом диапазоне [0, 100], что соответствует условию элемента. Тест явно проверяет сохранение значения (currentLevel = 0) и возврат корректного статуса (STATUS_OK), требуемого элементом. Цитаты из expected_result подтверждают выполнение обоих аспектов обязательства.
+Точные совпадения: STATUS_OK, currentLevel
+Числовой контекст: [{"parameter": "value", "value": "0", "lower": "0", "upper": "100", "inside": true, "position": "нижняя граница", "range_fully_tested": false}]
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(0)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 0; возвращён STATUS_OK"]}</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="b">
         <v>1</v>
@@ -1829,33 +4743,49 @@
       </c>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n"/>
+      <c r="S19" s="2" t="n"/>
+      <c r="T19" s="2" t="n"/>
+      <c r="U19" s="2" t="n"/>
+      <c r="V19" s="2" t="n"/>
+      <c r="W19" s="2" t="n"/>
+      <c r="X19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E002</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_BAD</t>
+          <t>TC_RANGE_02</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>не покрыт</t>
+          <t>покрыт</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Тест не проверяет возвращение STATUS_RANGE_ERROR и оставление currentLevel без изменения для значения value, которое меньше 0 или больше 100.
+          <t>Элемент требует сохранения значения в currentLevel и возврата STATUS_OK при входе 50 (в диапазоне 0-100). Тест предоставляет вход value=50, предусловие устанавливает начальное состояние, шаги включают вызов функции и проверку состояния/статуса. Ожидаемый результат теста (currentLevel = 50; возвращён STATUS_OK) семантически полностью покрывает обязательства элемента.
 Точные совпадения: STATUS_OK, currentLevel
-Отсутствующие токены: value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)"], "expected_result": ["Возвращён STATUS_OK; currentLevel = 101"]}</t>
+Числовой контекст: [{"parameter": "value", "value": "50", "lower": "0", "upper": "100", "inside": true, "position": "внутри", "range_fully_tested": false}]
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(50)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 50; возвращён STATUS_OK"]}</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F20" s="2" t="b">
         <v>1</v>
@@ -1867,33 +4797,49 @@
       </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="n"/>
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="n"/>
+      <c r="W20" s="2" t="n"/>
+      <c r="X20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E003</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_01</t>
+          <t>TC_RANGE_03</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>не покрыт</t>
+          <t>покрыт</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_01 проверяет только значение value = 0, которое находится в допустимом диапазоне от 0 до 100 включительно. Тест не покрывает значения, которые должны вызвать ошибку STATUS_RANGE_ERROR, такие как value &lt; 0 и value &gt; 100.
-Точные совпадения: 0, currentLevel
-Отсутствующие токены: 100, STATUS_RANGE_ERROR, value
-Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
+          <t>Тест TC_RANGE_03 полностью покрывает элемент DEMO_RANGE_001::E001. Входное значение value=100 находится в допустимом диапазоне [0, 100], что соответствует условию элемента. Тест явно проверяет сохранение значения (currentLevel = 100) и возврат правильного статуса (STATUS_OK), что подтверждается цитатами из шагов и ожидаемого результата.
+Точные совпадения: STATUS_OK, currentLevel
+Числовой контекст: [{"parameter": "value", "value": "100", "lower": "0", "upper": "100", "inside": true, "position": "верхняя граница", "range_fully_tested": false}]
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(100)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 100", "возвращён STATUS_OK"]}</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F21" s="2" t="b">
         <v>1</v>
@@ -1905,16 +4851,31 @@
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
+      <c r="T21" s="2" t="n"/>
+      <c r="U21" s="2" t="n"/>
+      <c r="V21" s="2" t="n"/>
+      <c r="W21" s="2" t="n"/>
+      <c r="X21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E003</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_02</t>
+          <t>TC_RANGE_04</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1924,14 +4885,15 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_02 проверяет только значение value = 50, которое находится в допустимом диапазоне от 0 до 100 включительно. Тест не покрывает случаи, когда value меньше 0 или больше 100, которые описаны в элементе DEMO_RANGE_001::E003.
+          <t>Тест TC_RANGE_04 проверяет ветвь для недопустимого значения value=-1 (меньше 0). Однако оцениваемый элемент DEMO_RANGE_001::E001 требует проверки поведения при допустимом значении (0 &lt;= value &lt;= 100), где ожидается сохранение value в currentLevel и возврат STATUS_OK. Входные данные теста (-1) противоречат условию применимости для данного элемента, что делает положительное покрытие невозможным.
 Точные совпадения: currentLevel
-Отсутствующие токены: 0, 100, STATUS_RANGE_ERROR, value
+Числовой контекст: [{"parameter": "value", "value": "-1", "lower": "0", "upper": "100", "inside": false, "position": "вне", "range_fully_tested": false}]
+Отсутствующие токены: STATUS_OK
 Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="b">
         <v>1</v>
@@ -1943,16 +4905,31 @@
       </c>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="n"/>
+      <c r="W22" s="2" t="n"/>
+      <c r="X22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E003</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_03</t>
+          <t>TC_RANGE_05</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1962,14 +4939,15 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_03 проверяет только значение value = 100 и не покрывает случаи, когда value меньше 0 или больше 100.
-Точные совпадения: 100, currentLevel
-Отсутствующие токены: 0, STATUS_RANGE_ERROR, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(100)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 100; возвращён STATUS_OK"]}</t>
+          <t>Элемент E001 требует сохранения переданного значения в currentLevel и возврата STATUS_OK при значении value от 0 до 100. Тест TC_RANGE_05 использует вход value=101, который выходит за границы диапазона элемента (больше 100). Согласно условию применимости, все условия all_true должны быть истинны для положительного покрытия ветки E001. Поскольку вход не соответствует диапазону [0, 100], этот тест проверяет ветку E002, а не E001. Следовательно, элемент E001 этим тестом не покрыт.
+Точные совпадения: currentLevel
+Числовой контекст: [{"parameter": "value", "value": "101", "lower": "0", "upper": "100", "inside": false, "position": "вне", "range_fully_tested": false}]
+Отсутствующие токены: STATUS_OK
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F23" s="2" t="b">
         <v>1</v>
@@ -1981,34 +4959,49 @@
       </c>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="n"/>
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="n"/>
+      <c r="W23" s="2" t="n"/>
+      <c r="X23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E003</t>
+          <t>DEMO_RANGE_001::E001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_04</t>
+          <t>TC_RANGE_BAD</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>требует проверки</t>
+          <t>не покрыт</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_04 проверяет ветвь, где value меньше 0. В тесте указано, что статус должен быть STATUS_RANGE_ERROR и currentLevel должен остаться без изменения. Это соответствует условию элемента E003, где указано, что если value меньше 0, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения.
-Точные совпадения: STATUS_RANGE_ERROR, currentLevel
-Отсутствующие токены: 0, 100, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(-1)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}
-Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 0, 100, value</t>
+          <t>Тест TC_RANGE_BAD использует вход value=101, который находится вне диапазона [0, 100] и соответствует условию элемента DEMO_RANGE_001::E002 (ошибочный статус), а не E001. Ожидаемый результат теста (STATUS_OK) прямо противоречит поведению, описанному в требовании для данного входа: 'Если value больше 100, компонент должен вернуть STATUS_RANGE_ERROR'. Следовательно, тест не покрывает элемент E001 и фактически проверяет противоположное поведение.
+Точные совпадения: STATUS_OK, currentLevel
+Числовой контекст: [{"parameter": "value", "value": "101", "lower": "0", "upper": "100", "inside": false, "position": "вне", "range_fully_tested": false}]
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="b">
         <v>1</v>
@@ -2020,30 +5013,45 @@
       </c>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="n"/>
+      <c r="W24" s="2" t="n"/>
+      <c r="X24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E003</t>
+          <t>DEMO_RANGE_001::E002</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_05</t>
+          <t>TC_RANGE_01</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>требует проверки</t>
+          <t>не покрыт</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_05 проверяет ветвь, где value больше 100. В тесте указано, что вызов SetLevel(101) должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения. Это соответствует условию элемента E003, где указано, что если value больше 100, компонент должен вернуть STATUS_RANGE_ERROR и оставить currentLevel без изменения.
-Точные совпадения: STATUS_RANGE_ERROR, currentLevel
-Отсутствующие токены: 0, 100, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}
-Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 0, 100, value</t>
+          <t>Тест TC_RANGE_01 проверяет ветвь с вводом value=0, который попадает в диапазон [0, 100]. Согласно условию применимости элемента E002 (value &lt; 0 ИЛИ value &gt; 100), данный тест не может покрыть требуемый элемент, так как предпосылки (вызов с аргументом вне диапазона) не выполняются. Тест возвращает STATUS_OK, что противоречит ожидаемому результату для элемента E002 (STATUS_RANGE_ERROR).
+Точные совпадения: 0, SetLevel, currentLevel, value
+Числовой контекст: [{"parameter": "value", "value": "0", "lower": "0", "upper": "100", "inside": true, "position": "нижняя граница", "range_fully_tested": false}]
+Отсутствующие токены: 100, STATUS_RANGE_ERROR
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -2059,16 +5067,31 @@
       </c>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="n"/>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n"/>
+      <c r="W25" s="2" t="n"/>
+      <c r="X25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E003</t>
+          <t>DEMO_RANGE_001::E002</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_BAD</t>
+          <t>TC_RANGE_02</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2078,14 +5101,15 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Тест не покрывает все возможные значения value, которые должны вызывать возврат STATUS_RANGE_ERROR. Также отсутствуют проверки для границ диапазона (0 и 100).
-Точные совпадения: currentLevel
-Отсутствующие токены: 0, 100, STATUS_RANGE_ERROR, value
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)"], "expected_result": ["Возвращён STATUS_OK; currentLevel = 101"]}</t>
+          <t>Элемент E002 требует проверки поведения при входе value &lt; 0 или value &gt; 100 (возврат STATUS_RANGE_ERROR и отсутствие изменения currentLevel). Тест TC_RANGE_02 использует вход value=50, который находится внутри допустимого диапазона [0, 100]. Следовательно, тест проверяет ветвь элемента E001, а не E002. Условия применимости для E002 (value &lt; 0 или value &gt; 100) явно нарушены входом теста.
+Точные совпадения: SetLevel, currentLevel, value
+Числовой контекст: [{"parameter": "value", "value": "50", "lower": "0", "upper": "100", "inside": true, "position": "внутри", "range_fully_tested": false}]
+Отсутствующие токены: 0, 100, STATUS_RANGE_ERROR
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="b">
         <v>1</v>
@@ -2097,30 +5121,45 @@
       </c>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n"/>
+      <c r="W26" s="2" t="n"/>
+      <c r="X26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E004</t>
+          <t>DEMO_RANGE_001::E002</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_01</t>
+          <t>TC_RANGE_03</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>требует проверки</t>
+          <t>не покрыт</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_01 проверяет нижнюю границу допустимого диапазона (value = 0), что соответствует условию в требовании. В результате теста currentLevel = 0 и возвращён STATUS_OK, что соответствует ожидаемому результату в требовании.
-Точные совпадения: 0
-Отсутствующие токены: 100
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(0)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 0; возвращён STATUS_OK"]}
-Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 100</t>
+          <t>Тест TC_RANGE_03 проверяет вход value=100, который попадает в диапазон [0; 100] (ветвь E001). Элемент DEMO_RANGE_001::E002 требует проверки условий 'value меньше 0' или 'value больше 100'. Входное значение 100 не удовлетворяет ни одному из этих условий, поэтому элемент не покрыт данным тестом.
+Точные совпадения: 100, SetLevel, currentLevel, value
+Числовой контекст: [{"parameter": "value", "value": "100", "lower": "0", "upper": "100", "inside": true, "position": "верхняя граница", "range_fully_tested": false}]
+Отсутствующие токены: 0, STATUS_RANGE_ERROR
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -2136,33 +5175,49 @@
       </c>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
+      <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="n"/>
+      <c r="U27" s="2" t="n"/>
+      <c r="V27" s="2" t="n"/>
+      <c r="W27" s="2" t="n"/>
+      <c r="X27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E004</t>
+          <t>DEMO_RANGE_001::E002</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_02</t>
+          <t>TC_RANGE_04</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>требует проверки</t>
+          <t>покрыт</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_02 покрывает только значение 50, которое находится в пределах диапазона от 0 до 100. Однако, согласно требованию, необходимо проверить все значения в этом диапазоне. Тест не покрывает граничные значения 0 и 100.
-Точные совпадения: нет
-Отсутствующие токены: 0, 100
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(50)", "Проверить currentLevel и возвращаемый статус"], "expected_result": ["currentLevel = 50; возвращён STATUS_OK"]}</t>
+          <t>Тест TC_RANGE_04 удовлетворяет условию применимости элемента DEMO_RANGE_001::E002 (вызов SetLevel с value &lt; 0). Входное значение -1 меньше нижней границы диапазона. Тест явно проверяет возврат STATUS_RANGE_ERROR и сохранение currentLevel на исходном значении (25), что полностью соответствует ожидаемому результату элемента.
+Точные совпадения: STATUS_RANGE_ERROR, SetLevel, currentLevel, value
+Числовой контекст: [{"parameter": "value", "value": "-1", "lower": "0", "upper": "100", "inside": false, "position": "вне", "range_fully_tested": false}]
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": [], "steps": ["Вызвать SetLevel(-1)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F28" s="2" t="b">
         <v>1</v>
@@ -2174,34 +5229,49 @@
       </c>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="n"/>
+      <c r="U28" s="2" t="n"/>
+      <c r="V28" s="2" t="n"/>
+      <c r="W28" s="2" t="n"/>
+      <c r="X28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E004</t>
+          <t>DEMO_RANGE_001::E002</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_03</t>
+          <t>TC_RANGE_05</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>требует проверки</t>
+          <t>не покрыт</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_03 проверяет значение value = 100, которое находится в пределах диапазона от 0 до 100 включительно. В соответствии с требованием, компонент должен сохранить value в поле currentLevel и вернуть STATUS_OK. Тест выполняет вызов SetLevel(100) и проверяет, что currentLevel = 100 и возвращённый статус STATUS_OK соответствует ожидаемому результату.
-Точные совпадения: 100
-Отсутствующие токены: 0
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(100)"], "expected_result": ["currentLevel = 100; возвращён STATUS_OK"]}
-Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 0</t>
+          <t>Элемент DEMO_RANGE_001::E002 требует проверки двух условий: value &lt; 0 ИЛИ value &gt; 100. Тест TC_RANGE_05 проверяет только одно условие (value = 101, что больше 100) и подтверждает ожидаемый результат для него. Однако второе условие (value &lt; 0) не покрыто данным тестом. Поскольку элемент охватывает оба случая, отсутствие теста для значения меньше 0 означает, что требование элемента не полностью выполнено набором доступных тестов.
+Точные совпадения: STATUS_RANGE_ERROR, SetLevel, currentLevel, value
+Числовой контекст: [{"parameter": "value", "value": "101", "lower": "0", "upper": "100", "inside": false, "position": "вне", "range_fully_tested": false}]
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="F29" s="2" t="b">
         <v>1</v>
@@ -2213,16 +5283,31 @@
       </c>
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
+      <c r="T29" s="2" t="n"/>
+      <c r="U29" s="2" t="n"/>
+      <c r="V29" s="2" t="n"/>
+      <c r="W29" s="2" t="n"/>
+      <c r="X29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E004</t>
+          <t>DEMO_RANGE_001::E002</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_04</t>
+          <t>TC_RANGE_BAD</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2232,14 +5317,15 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_04 проверяет только значение value = -1, которое находится за пределами допустимого диапазона. Тест не покрывает ни нижнюю, ни верхнюю границу диапазона (0 и 100), что соответствует условию элемента DEMO_RANGE_001::E004.
-Точные совпадения: нет
-Отсутствующие токены: 0, 100
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(-1)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
+          <t>Тест TC_RANGE_BAD проверяет вход value=101 (больше 100), что соответствует условию применимости для элемента E002. Однако ожидаемый результат в тесте ('STATUS_OK', 'currentLevel = 101') прямо противоречит требованию элемента, которое гласит, что при value &gt; 100 должен возвращаться 'STATUS_RANGE_ERROR' и 'currentLevel' должен остаться без изменения. Из-за этого противоречия между предикатом теста (ожидаемый результат) и целевым элементом положительного покрытия нет.
+Точные совпадения: SetLevel, currentLevel, value
+Числовой контекст: [{"parameter": "value", "value": "101", "lower": "0", "upper": "100", "inside": false, "position": "вне", "range_fully_tested": false}]
+Отсутствующие токены: STATUS_RANGE_ERROR
+Цитаты теста: {"preconditions": [], "steps": ["Вызвать SetLevel(101)"], "expected_result": []}</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F30" s="2" t="b">
         <v>1</v>
@@ -2251,33 +5337,48 @@
       </c>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="n"/>
+      <c r="U30" s="2" t="n"/>
+      <c r="V30" s="2" t="n"/>
+      <c r="W30" s="2" t="n"/>
+      <c r="X30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E004</t>
+          <t>DEMO_MODE_002::E001</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_05</t>
+          <t>TC_MODE_STANDBY</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>не покрыт</t>
+          <t>покрыт</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Тест TC_RANGE_05 проверяет значение value=101, которое находится за пределами диапазона от 0 до 100 включительно. Однако, согласно требованию, диапазон включает значения от 0 до 100 включительно. Тест не покрывает ни нижний ни верхний пределы диапазона, поэтому требование не полностью покрыто.
-Точные совпадения: нет
-Отсутствующие токены: 0, 100
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)", "Проверить статус и сохранность currentLevel"], "expected_result": ["Возвращён STATUS_RANGE_ERROR; currentLevel = 25"]}</t>
+          <t>Тест TC_MODE_STANDBY полностью покрывает элемент E001. Условие применимости (Вызов ReadSample и Режим STANDBY) выполнено: вход mode установлен в 'STANDBY'. Действие вызова функции подтверждено шагом 'Вызвать ReadSample'. Ожидаемые результаты (возврат STATUS_NOT_READY и отсутствие вызова StartADC) точно соответствуют требованиям элемента и ожидаемому результату теста.
+Точные совпадения: ReadSample, STANDBY, STATUS_NOT_READY, StartADC
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["Режим = STANDBY"], "steps": ["Очистить журнал вызовов", "Вызвать ReadSample", "Проверить статус и журнал StartADC"], "expected_result": ["Возвращён STATUS_NOT_READY; StartADC не вызван"]}</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F31" s="2" t="b">
         <v>1</v>
@@ -2289,16 +5390,31 @@
       </c>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="n"/>
+      <c r="R31" s="2" t="n"/>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n"/>
+      <c r="U31" s="2" t="n"/>
+      <c r="V31" s="2" t="n"/>
+      <c r="W31" s="2" t="n"/>
+      <c r="X31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DEMO_RANGE_001::E004</t>
+          <t>DEMO_MODE_002::E001</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TC_RANGE_BAD</t>
+          <t>TC_MODE_ACTIVE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2308,14 +5424,14 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Тест не покрывает ни нижний ни верхний пределы диапазона от 0 до 100 включительно. Он проверяет значение, которое находится за пределами этого диапазона (101).
-Точные совпадения: нет
-Отсутствующие токены: 0, 100
-Цитаты теста: {"preconditions": ["currentLevel = 25"], "steps": ["Вызвать SetLevel(101)"], "expected_result": ["Возвращён STATUS_OK; currentLevel = 101"]}</t>
+          <t>Элемент DEMO_MODE_002::E001 требует поведения в режиме STANDBY (возврат STATUS_NOT_READY, отсутствие вызова StartADC). Тест TC_MODE_ACTIVE явно задает precondition 'Режим = ACTIVE'. Поскольку условие применимости (all_true) содержит 'Режим STANDBY', а тест выполняет действия в режиме ACTIVE, условия элемента не выполняются. Следовательно, элемент не покрыт данным тестом.
+Точные совпадения: ReadSample, StartADC
+Отсутствующие токены: STANDBY, STATUS_NOT_READY
+Цитаты теста: {"preconditions": ["Режим = ACTIVE", "ADC_READY = 1"], "steps": ["Вызвать ReadSample"], "expected_result": []}</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F32" s="2" t="b">
         <v>1</v>
@@ -2327,6 +5443,2252 @@
       </c>
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="n"/>
+      <c r="U32" s="2" t="n"/>
+      <c r="V32" s="2" t="n"/>
+      <c r="W32" s="2" t="n"/>
+      <c r="X32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002::E001</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>TC_MODE_UNSPEC</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Элемент DEMO_MODE_002::E001 требует проверки поведения компонента в режиме STANDBY при вызове ReadSample (возврат STATUS_NOT_READY, отсутствие вызова StartADC). Представленный тест TC_MODE_UNSPEC явно задает precondition 'Режим = ACTIVE' и проверяет поведение при 'ADC_READY = 0'. Это противоречит условию применимости элемента (все условия all_true должны быть истинны), так как режим не соответствует STANDBY. Следовательно, тест не покрывает данный элемент.
+Точные совпадения: ReadSample
+Отсутствующие токены: STANDBY, STATUS_NOT_READY, StartADC
+Цитаты теста: {"preconditions": ["Режим = ACTIVE", "ADC_READY = 0"], "steps": ["Вызвать ReadSample"], "expected_result": ["Возвращён STATUS_TIMEOUT"]}</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="n"/>
+      <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="n"/>
+      <c r="U33" s="2" t="n"/>
+      <c r="V33" s="2" t="n"/>
+      <c r="W33" s="2" t="n"/>
+      <c r="X33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002::E002</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>TC_MODE_STANDBY</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_MODE_STANDBY проверяет поведение компонента в режиме STANDBY (условие all_true: 'Режим ACTIVE' ложно). В соответствии с требованием DEMO_MODE_002, при вызове ReadSample в режиме STANDBY компонент не должен вызывать StartADC(), но может возвращать STATUS_NOT_READY. Однако рассматриваемый элемент E002 требует именно выполнения действия 'вызвать StartADC()'. Поскольку тест намеренно блокирует условие 'Режим ACTIVE', он не выполняет требуемое действие для элемента E002, а проверяет обратное поведение (отсутствие вызова). Следовательно, положительного покрытия элемента 'Вызов StartADC()' нет.
+Точные совпадения: ReadSample, StartADC
+Отсутствующие токены: ACTIVE
+Цитаты теста: {"preconditions": ["Режим = STANDBY"], "steps": ["Очистить журнал вызовов", "Вызвать ReadSample", "Проверить статус и журнал StartADC"], "expected_result": ["Возвращён STATUS_NOT_READY; StartADC не вызван"]}</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n"/>
+      <c r="U34" s="2" t="n"/>
+      <c r="V34" s="2" t="n"/>
+      <c r="W34" s="2" t="n"/>
+      <c r="X34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002::E002</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>TC_MODE_ACTIVE</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Тестовый случай 'TC_MODE_ACTIVE' корректно устанавливает все необходимые условия для элемента E002: вызывается ReadSample (указано в шагах), режим установлен в ACTIVE (в preconditions и input_data), а переменная ADC_READY равна 1. Это соответствует условию применимости элемента [Вызов ReadSample, Режим ACTIVE]. Действие 'вызвать StartADC() без аргументов' прямо указано как ожидаемый результат в expected_result теста. Таким образом, элемент покрыт.
+Точные совпадения: ACTIVE, ReadSample, StartADC
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["Режим = ACTIVE", "ADC_READY = 1"], "steps": ["Вызвать ReadSample", "Зафиксировать вызовы StartADC и ReadADC и возвращаемое значение"], "expected_result": ["StartADC() вызван без аргументов"]}</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="n"/>
+      <c r="U35" s="2" t="n"/>
+      <c r="V35" s="2" t="n"/>
+      <c r="W35" s="2" t="n"/>
+      <c r="X35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002::E002</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>TC_MODE_UNSPEC</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Тест не покрывает элемент E002. Согласно требованию и условию применимости (all_true: ['Вызов ReadSample', 'Режим ACTIVE']), при вызове ReadSample в режиме ACTIVE компонент обязан вызвать StartADC(). Однако тест имеет вход ADC_READY = 0, что переводит выполнение логики в ветку, где поведение не определено (по тексту требования: 'Поведение в режиме ACTIVE при ADC_READY, отличном от 1, не определено'). В этой неопределенной ветке вызов StartADC() может произойти или не произойти. Тест ожидает STATUS_TIMEOUT, что является неопределенным результатом для данного элемента и входа, а не подтвержденным ожидаемым результатом из требования. Следовательно, требование на вызов StartADC() в этом конкретном сценарии не доказано.
+Точные совпадения: ACTIVE, ReadSample
+Отсутствующие токены: StartADC
+Цитаты теста: {"preconditions": ["Режим = ACTIVE", "ADC_READY = 0"], "steps": ["Вызвать ReadSample"], "expected_result": ["Возвращён STATUS_TIMEOUT"]}</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
+      <c r="T36" s="2" t="n"/>
+      <c r="U36" s="2" t="n"/>
+      <c r="V36" s="2" t="n"/>
+      <c r="W36" s="2" t="n"/>
+      <c r="X36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002::E003</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>TC_MODE_STANDBY</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_MODE_STANDBY проверяет только режим STANDBY. Элемент E003 требует выполнения в режиме ACTIVE при условии ADC_READY=1. Тест не устанавливает преусловие 'Режим = ACTIVE' и не задает входное значение ADC_READY=1 (установлен только mode: STANDBY). Следовательно, тест не может выполнить шаги вызова ReadADC() или проверки возврата значения для данного элемента.
+Точные совпадения: ReadSample
+Отсутствующие токены: 1, ACTIVE, ADC_READY, ReadADC
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="n"/>
+      <c r="T37" s="2" t="n"/>
+      <c r="U37" s="2" t="n"/>
+      <c r="V37" s="2" t="n"/>
+      <c r="W37" s="2" t="n"/>
+      <c r="X37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002::E003</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>TC_MODE_ACTIVE</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_MODE_ACTIVE полностью покрывает элемент E003. Условия применимости (Вызов ReadSample, Режим ACTIVE, ADC_READY равно 1) выполнены через входные данные input_data и preconditions. Действие вызова функции ReadADC без аргументов подтверждается ожидаемым результатом, где явно указано 'ReadADC() вызван без аргументов'. Ожидаемый результат также содержит проверку возвращаемого значения (42), что соответствует требованию вернуть прочитанное значение.
+Точные совпадения: 1, ACTIVE, ADC_READY, ReadADC, ReadSample
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["Режим = ACTIVE", "ADC_READY = 1", "ReadADC возвращает 42"], "steps": ["Зафиксировать вызовы StartADC и ReadADC и возвращаемое значение"], "expected_result": ["StartADC() вызван без аргументов; ReadADC() вызван без аргументов; возвращено 42"]}</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n"/>
+      <c r="S38" s="2" t="n"/>
+      <c r="T38" s="2" t="n"/>
+      <c r="U38" s="2" t="n"/>
+      <c r="V38" s="2" t="n"/>
+      <c r="W38" s="2" t="n"/>
+      <c r="X38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002::E003</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>TC_MODE_UNSPEC</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Тестовый сценарий явно задает условие ADC_READY = 0 (не 1). Согласно требованию и элементу DEMO_MODE_002::E003, вызов ReadADC() должен происходить только при условии 'если ADC_READY равно 1'. Следовательно, в данном тесте действие 'вызвать ReadADC()' не выполняется. Ожидаемый результат теста (STATUS_TIMEOUT) также не соответствует требуемому результату элемента (возврат прочитанного значения). Тест проверяет поведение для ветви 'неготового' ADC, которая не входит в область покрытия текущего элемента E003.
+Точные совпадения: ACTIVE, ADC_READY, ReadSample
+Отсутствующие токены: 1, ReadADC
+Цитаты теста: {"preconditions": ["Режим = ACTIVE", "ADC_READY = 0"], "steps": ["Вызвать ReadSample"], "expected_result": ["Возвращён STATUS_TIMEOUT"]}</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="n"/>
+      <c r="U39" s="2" t="n"/>
+      <c r="V39" s="2" t="n"/>
+      <c r="W39" s="2" t="n"/>
+      <c r="X39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E001</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FIRST</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Элемент E001 требует вызова SendFrame(frame) при условии 'До получения результата SEND_OK'. Тест TC_LOOP_FIRST настраивает входные данные так, что SendFrame сразу возвращает 'SEND_OK' ('SendFrame_returns': 'SEND_OK'). Это создает конфликт условий: действие выполняется, но условие 'до получения результата' выполняется только мгновенно или не выполняется в контексте цикла. Хотя тест проверяет количество вызовов (один раз), отсутствие доказательства того, как работает заглушка при последующих попытках (или что цикл вообще инициируется с ожиданием ответа != SEND_OK) делает покрытие неполным для условия 'до получения результата'. Более того, expected_result утверждает, что вызов был 1 раз, но не подтверждает выполнение условия цикла 'пока результат != SEND_OK', а сразу получает его.
+Точные совпадения: RetrySend, SEND_OK, SendFrame, frame
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["frame подготовлен", "Заглушка SendFrame возвращает заданную последовательность"], "steps": ["Проверить число вызовов SendFrame(frame) и статус RetrySend"], "expected_result": ["SendFrame(frame) вызван 1 раз; RetrySend вернул STATUS_OK; дополнительных вызовов нет"]}</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
+      <c r="Q40" s="2" t="n"/>
+      <c r="R40" s="2" t="n"/>
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="2" t="n"/>
+      <c r="U40" s="2" t="n"/>
+      <c r="V40" s="2" t="n"/>
+      <c r="W40" s="2" t="n"/>
+      <c r="X40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E001</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_THIRD</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Элемент требует вызова SendFrame до получения SEND_OK. Тестовый вход (SEND_ERROR, SEND_ERROR, SEND_OK) гарантирует выполнение условия 'До получения результата SEND_OK' ровно 3 раза. Шаги теста содержат действие 'Проверить число вызовов', что подтверждает намерение проверить элемент, но в предоставленных цитатах шагов нет явного утверждения о факте проверки именно числа вызовов (например, 'подтвердить, что вызовов ровно 3'). Однако ожидаемый результат явно фиксирует факт выполнения требования ('SendFrame(frame) вызван 3 раз'), что является достаточным доказательством покрытия действия для данного входа. Условие применимости выполнено: функция вызвана до получения успеха.
+Точные совпадения: RetrySend, SEND_OK, SendFrame, frame
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["Заглушка SendFrame возвращает заданную последовательность"], "steps": [], "expected_result": ["SendFrame(frame) вызван 3 раз; RetrySend вернул STATUS_OK; дополнительных вызовов нет"]}
+Проверка непротиворечивости: Нет цитат действий или ожидаемого результата</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
+      <c r="Q41" s="2" t="n"/>
+      <c r="R41" s="2" t="n"/>
+      <c r="S41" s="2" t="n"/>
+      <c r="T41" s="2" t="n"/>
+      <c r="U41" s="2" t="n"/>
+      <c r="V41" s="2" t="n"/>
+      <c r="W41" s="2" t="n"/>
+      <c r="X41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E001</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FAIL</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_LOOP_FAIL проверяет элемент DEMO_LOOP_003::E001 (обязательство вызывать SendFrame до SEND_OK). Условия применимости истинны: функция RetrySend вызывается, а результат SEND_OK еще не получен (тест симулирует сценарий 3-х ошибок). Тест подтверждает выполнение требования через проверку количества вызовов (3 раза) и отсутствия дополнительных вызовов после исчерпания лимита.
+Точные совпадения: RetrySend, SendFrame, frame
+Отсутствующие токены: SEND_OK
+Цитаты теста: {"preconditions": ["frame подготовлен", "Заглушка SendFrame возвращает заданную последовательность"], "steps": ["Вызвать RetrySend", "Проверить число вызовов SendFrame(frame) и статус RetrySend"], "expected_result": ["SendFrame(frame) вызван 3 раз", "RetrySend вернул STATUS_SEND_ERROR; дополнительных вызовов нет"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: SEND_OK</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
+      <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="n"/>
+      <c r="S42" s="2" t="n"/>
+      <c r="T42" s="2" t="n"/>
+      <c r="U42" s="2" t="n"/>
+      <c r="V42" s="2" t="n"/>
+      <c r="W42" s="2" t="n"/>
+      <c r="X42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E001</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_PARTIAL</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Элемент E001 требует выполнения действия 'вызывать SendFrame(frame)' до получения результата SEND_OK и при вызове функции RetrySend. Тест TC_LOOP_PARTIAL имеет условие применимости 'SendFrame всегда возвращает SEND_ERROR'. Это противоречит условию применимости элемента 'До получения результата SEND_OK', так как в данном сценарии SEND_OK никогда не будет получен, что делает невозможным выполнение требуемого действия 'вызывать SendFrame' именно до момента получения успеха (цикл может завершиться по таймауту или лимиту попыток, но логика элемента описывает процесс достижения успеха). Более того, тест проверяет ветку возврата STATUS_SEND_ERROR (элемент E004), а не выполнение цикла вызовов SendFrame до успеха. Цитат подтверждения выполнения действия 'вызывать SendFrame(frame)' в контексте условия 'до получения SEND_OK' в шагах или ожидаемом результате теста отсутствует.
+Точные совпадения: RetrySend, SendFrame
+Отсутствующие токены: SEND_OK, frame
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="n"/>
+      <c r="U43" s="2" t="n"/>
+      <c r="V43" s="2" t="n"/>
+      <c r="W43" s="2" t="n"/>
+      <c r="X43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E001</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_BAD</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_LOOP_BAD проверяет ветку, где все 3 вызова возвращают SEND_ERROR (условие для элемента E004), но ожидает результат, противоречащий логике требования: тест требует 'SendFrame(frame) вызван 4 раза', тогда как требование строго ограничивает количество вызовов 'не более 3 раз'. Следовательно, элемент E001 ('Компонент должен вызывать SendFrame(frame)... не более 3 раз') положительным образом покрыт этим тестом не может быть, так как поведение теста (вызов 4 раза) является нарушением условия применимости элемента.
+Точные совпадения: RetrySend, SendFrame, frame
+Отсутствующие токены: SEND_OK
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F44" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="n"/>
+      <c r="U44" s="2" t="n"/>
+      <c r="V44" s="2" t="n"/>
+      <c r="W44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E002</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FIRST</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_LOOP_FIRST полностью покрывает элемент E002 ('Повторные вызовы SendFrame запрещены') и связанный с ним результат возврата STATUS_OK (E003). Входное условие 'SendFrame_returns: SEND_OK' (из input_data) обеспечивает выполнение условия 'После получения результата SEND_OK'. Шаг 'Проверить число вызовов... и статус' соответствует ожидаемому результату, где явно указано отсутствие дополнительных вызовов и возврат STATUS_OK. Прямые цитаты из expected_result подтверждают оба аспекта элемента.
+Точные совпадения: RetrySend, SEND_OK, SendFrame
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["Заглушка SendFrame возвращает заданную последовательность"], "steps": ["Проверить число вызовов SendFrame(frame) и статус RetrySend"], "expected_result": ["SendFrame(frame) вызван 1 раз; RetrySend вернул STATUS_OK; дополнительных вызовов нет"]}</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F45" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
+      <c r="Q45" s="2" t="n"/>
+      <c r="R45" s="2" t="n"/>
+      <c r="S45" s="2" t="n"/>
+      <c r="T45" s="2" t="n"/>
+      <c r="U45" s="2" t="n"/>
+      <c r="V45" s="2" t="n"/>
+      <c r="W45" s="2" t="n"/>
+      <c r="X45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E002</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_THIRD</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_LOOP_THIRD удовлетворяет условиям применимости элемента DEMO_LOOP_003::E002 ('При вызове функции RetrySend', 'После получения результата SEND_OK'). Входные данные теста задают последовательность возвратов, где третий вызов возвращает SEND_OK, что активирует ветку требования. Действия теста включают проверку числа вызовов и статуса, а ожидаемый результат подтверждает выполнение обязательств: статус STATUS_OK и отсутствие дополнительных вызовов после успеха.
+Точные совпадения: RetrySend, SEND_OK, SendFrame
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["Заглушка SendFrame возвращает заданную последовательность"], "steps": ["Проверить число вызовов SendFrame(frame) и статус RetrySend"], "expected_result": ["SendFrame(frame) вызван 3 раз; RetrySend вернул STATUS_OK; дополнительных вызовов нет"]}</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F46" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
+      <c r="Q46" s="2" t="n"/>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="n"/>
+      <c r="T46" s="2" t="n"/>
+      <c r="U46" s="2" t="n"/>
+      <c r="V46" s="2" t="n"/>
+      <c r="W46" s="2" t="n"/>
+      <c r="X46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E002</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FAIL</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Элемент требует проверки поведения системы после получения результата SEND_OK (запрет повторных вызовов) и возврата STATUS_OK. Тест TC_LOOP_FAIL намеренно симулирует сценарий, где все три попытки заканчиваются ошибкой (SEND_ERROR). В этом случае условие применимости элемента ('После получения результата SEND_OK') никогда не выполняется, так как функция завершается до получения успешного ответа. Следовательно, поведение 'запрета повторных вызовов' в контексте успеха и возврат STATUS_OK не могут быть проверены данным тестом.
+Точные совпадения: RetrySend, SendFrame
+Отсутствующие токены: SEND_OK
+Цитаты теста: {"preconditions": ["Заглушка SendFrame возвращает заданную последовательность"], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="n"/>
+      <c r="Q47" s="2" t="n"/>
+      <c r="R47" s="2" t="n"/>
+      <c r="S47" s="2" t="n"/>
+      <c r="T47" s="2" t="n"/>
+      <c r="U47" s="2" t="n"/>
+      <c r="V47" s="2" t="n"/>
+      <c r="W47" s="2" t="n"/>
+      <c r="X47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E002</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_PARTIAL</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_LOOP_PARTIAL проверяет сценарий, где SendFrame возвращает SEND_ERROR. Это соответствует элементу E004 (ожидаемый результат STATUS_SEND_ERROR), но не покрывает элемент E002. Для покрытия элемента 'Повторные вызовы SendFrame запрещены' (E002) необходимо наличие условия 'После получения результата SEND_OK', которое отсутствует в Preconditions теста и не достигается в Steps, так как входные данные фиксируют возврат SEND_ERROR. Следовательно, условие применимости для E002 ('После получения результата SEND_OK') является ложным в данном контексте.
+Точные совпадения: RetrySend, SendFrame
+Отсутствующие токены: SEND_OK
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F48" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="n"/>
+      <c r="Q48" s="2" t="n"/>
+      <c r="R48" s="2" t="n"/>
+      <c r="S48" s="2" t="n"/>
+      <c r="T48" s="2" t="n"/>
+      <c r="U48" s="2" t="n"/>
+      <c r="V48" s="2" t="n"/>
+      <c r="W48" s="2" t="n"/>
+      <c r="X48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E002</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_BAD</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Тестовый случай TC_LOOP_BAD нацелен на сценарий, когда SendFrame всегда возвращает SEND_ERROR. Это противоречит условиям применимости элемента E002 ('После получения результата SEND_OK'), так как в этом сценарии результат SEND_OK никогда не достигается. Следовательно, ветка кода, защищающая от повторных вызовов после успеха, в данном тесте не исполняется. Тест проверяет другую ветку (все ошибки), но не покрывает требование о запрете повторных вызовов после успешного завершения.
+Точные совпадения: RetrySend, SendFrame
+Отсутствующие токены: SEND_OK
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="n"/>
+      <c r="Q49" s="2" t="n"/>
+      <c r="R49" s="2" t="n"/>
+      <c r="S49" s="2" t="n"/>
+      <c r="T49" s="2" t="n"/>
+      <c r="U49" s="2" t="n"/>
+      <c r="V49" s="2" t="n"/>
+      <c r="W49" s="2" t="n"/>
+      <c r="X49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E003</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FIRST</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Элемент требует возврата STATUS_OK после получения SEND_OK. Тест обеспечивает условие применимости (вызов функции, получение SEND_OK) через precondition 'Заглушка SendFrame возвращает заданную последовательность'. Шаг 'Проверить число вызовов SendFrame(frame) и статус RetrySend' и ожидаемый результат 'RetrySend вернул STATUS_OK' прямо покрывают требование возврата статуса.
+Точные совпадения: RetrySend, SEND_OK, STATUS_OK
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["Заглушка SendFrame возвращает заданную последовательность"], "steps": ["Проверить число вызовов SendFrame(frame) и статус RetrySend"], "expected_result": ["RetrySend вернул STATUS_OK"]}</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F50" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="n"/>
+      <c r="Q50" s="2" t="n"/>
+      <c r="R50" s="2" t="n"/>
+      <c r="S50" s="2" t="n"/>
+      <c r="T50" s="2" t="n"/>
+      <c r="U50" s="2" t="n"/>
+      <c r="V50" s="2" t="n"/>
+      <c r="W50" s="2" t="n"/>
+      <c r="X50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E003</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_THIRD</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_LOOP_THIRD покрывает элемент DEMO_LOOP_003::E003. Входные данные (input_data) задают сценарий, при котором SendFrame возвращает SEND_ERROR дважды и затем SEND_OK, что соответствует условию элемента "После получения результата SEND_OK". Шаг теста содержит действие проверки статуса, а ожидаемый результат явно подтверждает выполнение обязательства через цитату "RetrySend вернул STATUS_OK".
+Точные совпадения: RetrySend, SEND_OK, STATUS_OK
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["frame подготовлен", "Заглушка SendFrame возвращает заданную последовательность"], "steps": ["Проверить число вызовов SendFrame(frame) и статус RetrySend"], "expected_result": ["SendFrame(frame) вызван 3 раз; RetrySend вернул STATUS_OK; дополнительных вызовов нет"]}</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
+      <c r="Q51" s="2" t="n"/>
+      <c r="R51" s="2" t="n"/>
+      <c r="S51" s="2" t="n"/>
+      <c r="T51" s="2" t="n"/>
+      <c r="U51" s="2" t="n"/>
+      <c r="V51" s="2" t="n"/>
+      <c r="W51" s="2" t="n"/>
+      <c r="X51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E003</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FAIL</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Элемент DEMO_LOOP_003::E003 требует возврата STATUS_OK при условии получения результата SEND_OK. Представленный тест TC_LOOP_FAIL настроен на сценарий, где все три вызова завершаются SEND_ERROR (input_data: 'SendFrame_returns': 'SEND_ERROR, SEND_ERROR, SEND_ERROR'). Согласно требованию, в этом случае функция должна вернуть STATUS_SEND_ERROR, а не STATUS_OK. Следовательно, данный входной данные и ожидаемый результат теста противоречат условиям применимости элемента (all_true содержит 'После получения результата SEND_OK'), что делает положительное покрытие невозможным без изменения входных данных теста.
+Точные совпадения: RetrySend
+Отсутствующие токены: SEND_OK, STATUS_OK
+Цитаты теста: {"preconditions": ["Заглушка SendFrame возвращает заданную последовательность"], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F52" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="n"/>
+      <c r="Q52" s="2" t="n"/>
+      <c r="R52" s="2" t="n"/>
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="2" t="n"/>
+      <c r="U52" s="2" t="n"/>
+      <c r="V52" s="2" t="n"/>
+      <c r="W52" s="2" t="n"/>
+      <c r="X52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E003</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_PARTIAL</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Тестовый случай не покрывает элемент E003, так как предусловие теста ('SendFrame всегда возвращает SEND_ERROR') противоречит условию применимости элемента ('После получения результата SEND_OK'). В данном тесте функция никогда не получит статус SEND_OK, поэтому выполнение требования о возврате STATUS_OK после успешного завершения невозможно проверить.
+Точные совпадения: RetrySend
+Отсутствующие токены: SEND_OK, STATUS_OK
+Цитаты теста: {"preconditions": ["SendFrame всегда возвращает SEND_ERROR"], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="n"/>
+      <c r="Q53" s="2" t="n"/>
+      <c r="R53" s="2" t="n"/>
+      <c r="S53" s="2" t="n"/>
+      <c r="T53" s="2" t="n"/>
+      <c r="U53" s="2" t="n"/>
+      <c r="V53" s="2" t="n"/>
+      <c r="W53" s="2" t="n"/>
+      <c r="X53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E003</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_BAD</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Элемент E003 требует выполнения действия 'После получения результата SEND_OK' для возврата STATUS_OK. Тест TC_LOOP_BAD использует условие предпосылки 'SendFrame всегда возвращает SEND_ERROR', что делает невозможным получение результата SEND_OK в рамках этого теста. Следовательно, ключевое условие применимости элемента не выполняется. Ожидаемый результат теста (STATUS_SEND_ERROR) соответствует элементу E004, а не E003.
+Точные совпадения: RetrySend
+Отсутствующие токены: SEND_OK, STATUS_OK
+Цитаты теста: {"preconditions": ["SendFrame всегда возвращает SEND_ERROR"], "steps": ["Вызвать RetrySend", "Подсчитать вызовы SendFrame(frame)"], "expected_result": ["SendFrame(frame) вызван 4 раза; возвращён STATUS_SEND_ERROR"]}</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F54" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n"/>
+      <c r="Q54" s="2" t="n"/>
+      <c r="R54" s="2" t="n"/>
+      <c r="S54" s="2" t="n"/>
+      <c r="T54" s="2" t="n"/>
+      <c r="U54" s="2" t="n"/>
+      <c r="V54" s="2" t="n"/>
+      <c r="W54" s="2" t="n"/>
+      <c r="X54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E004</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FIRST</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_LOOP_FIRST проверяет сценарий успешного завершения (один вызов возвращает SEND_OK), что приводит к возврату STATUS_OK. Это не соответствует условию элемента E004, требующему, чтобы все три вызова завершились SEND_ERROR. Тест не содержит входных данных или шагов, имитирующих три последовательные ошибки, и не проверяет возврат STATUS_SEND_ERROR.
+Точные совпадения: RetrySend
+Отсутствующие токены: 3, SEND_ERROR, STATUS_SEND_ERROR
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="n"/>
+      <c r="Q55" s="2" t="n"/>
+      <c r="R55" s="2" t="n"/>
+      <c r="S55" s="2" t="n"/>
+      <c r="T55" s="2" t="n"/>
+      <c r="U55" s="2" t="n"/>
+      <c r="V55" s="2" t="n"/>
+      <c r="W55" s="2" t="n"/>
+      <c r="X55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E004</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_THIRD</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_LOOP_THIRD проверяет сценарий, при котором первые два вызова возвращают SEND_ERROR, а третий — SEND_OK. В этом случае требование предписывает возврат STATUS_OK (элемент E003), а не STATUS_SEND_ERROR. Элемент DEMO_LOOP_003::E004 требует возврата STATUS_SEND_ERROR только в том случае, если все 3 вызова завершатся с ошибкой (SEND_ERROR). Входные данные теста ('SEND_ERROR, SEND_OK') противоречат условию применимости элемента (все 3 вызова должны быть SEND_ERROR), поэтому элемент не покрыт.
+Точные совпадения: 3, RetrySend, SEND_ERROR
+Отсутствующие токены: STATUS_SEND_ERROR
+Цитаты теста: {"preconditions": [], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="n"/>
+      <c r="Q56" s="2" t="n"/>
+      <c r="R56" s="2" t="n"/>
+      <c r="S56" s="2" t="n"/>
+      <c r="T56" s="2" t="n"/>
+      <c r="U56" s="2" t="n"/>
+      <c r="V56" s="2" t="n"/>
+      <c r="W56" s="2" t="n"/>
+      <c r="X56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E004</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_FAIL</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Тест обеспечивает полное покрытие элемента E004. Входные данные 'SendFrame_returns: SEND_ERROR, SEND_ERROR, SEND_ERROR' соответствуют условию 'Если все 3 вызова завершились SEND_ERROR'. Шаг проверки статуса и ожидаемый результат подтверждают выполнение обязательства возврата STATUS_SEND_ERROR.
+Точные совпадения: 3, RetrySend, SEND_ERROR, STATUS_SEND_ERROR
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["Заглушка SendFrame возвращает заданную последовательность"], "steps": ["Проверить число вызовов SendFrame(frame) и статус RetrySend"], "expected_result": ["RetrySend вернул STATUS_SEND_ERROR"]}</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
+      <c r="P57" s="2" t="n"/>
+      <c r="Q57" s="2" t="n"/>
+      <c r="R57" s="2" t="n"/>
+      <c r="S57" s="2" t="n"/>
+      <c r="T57" s="2" t="n"/>
+      <c r="U57" s="2" t="n"/>
+      <c r="V57" s="2" t="n"/>
+      <c r="W57" s="2" t="n"/>
+      <c r="X57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E004</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_PARTIAL</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_LOOP_PARTIAL накрывает ветку элемента E004 (возврат STATUS_SEND_ERROR) при условии, что SendFrame возвращает ошибку. Preconditions теста ('SendFrame всегда возвращает SEND_ERROR') гарантируют выполнение условия 'Если все 3 вызова завершились SEND_ERROR', так как функция RetrySend вызывает SendFrame не более 3 раз. Шаг теста ('Вызвать RetrySend') инициирует этот процесс. Ожидаемый результат ('RetrySend вернул STATUS_SEND_ERROR') точно соответствует требованию элемента. Однако тест описывает общий сценарий без явного указания на то, что именно три вызова произошли (хотя логика функции это подразумевает), и не проверяет поведение при смешанных результатах или остановке после SEND_OK, но для конкретного элемента E004 доказательств достаточно.
+Точные совпадения: RetrySend, SEND_ERROR, STATUS_SEND_ERROR
+Отсутствующие токены: 3
+Цитаты теста: {"preconditions": ["SendFrame всегда возвращает SEND_ERROR"], "steps": ["Вызвать RetrySend"], "expected_result": ["RetrySend вернул STATUS_SEND_ERROR"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 3</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F58" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
+      <c r="P58" s="2" t="n"/>
+      <c r="Q58" s="2" t="n"/>
+      <c r="R58" s="2" t="n"/>
+      <c r="S58" s="2" t="n"/>
+      <c r="T58" s="2" t="n"/>
+      <c r="U58" s="2" t="n"/>
+      <c r="V58" s="2" t="n"/>
+      <c r="W58" s="2" t="n"/>
+      <c r="X58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_LOOP_003::E004</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOOP_BAD</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Тест проверяет ветку возврата STATUS_SEND_ERROR, однако вводит противоречие с условиями применимости элемента (DEMO_LOOP_003::E004). Условие применимости требует, чтобы 'все 3 вызова завершились SEND_ERROR'. Тестовое условие ('SendFrame всегда возвращает SEND_ERROR') и ожидаемый результат ('вызван 4 раза') нарушают ограничение на количество попыток (не более 3), описанное в требовании. Согласно логике требования, 4-й вызов не должен произойти, а функция должна завершиться после 3-го. Следовательно, ожидаемый результат теста ('вызван 4 раза') является неопределенным или ошибочным с точки зрения спецификации, что делает доказательство покрытия невозможным без ручной проверки корректности имитации отказа в тесте.
+Точные совпадения: RetrySend, SEND_ERROR, STATUS_SEND_ERROR
+Отсутствующие токены: 3
+Цитаты теста: {"preconditions": ["SendFrame всегда возвращает SEND_ERROR"], "steps": ["Вызвать RetrySend", "Подсчитать вызовы SendFrame(frame)"], "expected_result": ["SendFrame(frame) вызван 4 раза; возвращён STATUS_SEND_ERROR"]}</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F59" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="n"/>
+      <c r="P59" s="2" t="n"/>
+      <c r="Q59" s="2" t="n"/>
+      <c r="R59" s="2" t="n"/>
+      <c r="S59" s="2" t="n"/>
+      <c r="T59" s="2" t="n"/>
+      <c r="U59" s="2" t="n"/>
+      <c r="V59" s="2" t="n"/>
+      <c r="W59" s="2" t="n"/>
+      <c r="X59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004::E001</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>TC_TIME_9</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_TIME_9 проверяет элемент DEMO_TIME_004::E002 (отрицательный случай), а не элемент DEMO_TIME_004::E001. Входное значение elapsed_ms=9 меньше 10, что противоречит условию применимости для E001 (elapsed_ms &gt;= 10). Следовательно, тест не может доказать выполнение обязательства по вызову PollSensor при значении &gt;= 10.
+Точные совпадения: HandleTick, PollSensor, elapsed_ms
+Отсутствующие токены: 10
+Цитаты теста: {"preconditions": ["Журнал PollSensor очищен"], "steps": [], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="n"/>
+      <c r="Q60" s="2" t="n"/>
+      <c r="R60" s="2" t="n"/>
+      <c r="S60" s="2" t="n"/>
+      <c r="T60" s="2" t="n"/>
+      <c r="U60" s="2" t="n"/>
+      <c r="V60" s="2" t="n"/>
+      <c r="W60" s="2" t="n"/>
+      <c r="X60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004::E001</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>TC_TIME_10</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_TIME_10 полностью покрывает элемент DEMO_TIME_004::E001. Установлены все необходимые условия: вызов функции HandleTick и значение elapsed_ms равно 10 (удовлетворяет условию &gt;= 10). Шаг теста явно указывает на выполнение действия с указанным входным параметром, а ожидаемый результат точно соответствует требованию о вызове ровно одного раза.
+Точные совпадения: 10, HandleTick, PollSensor, elapsed_ms
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["Журнал PollSensor очищен"], "steps": ["Вызвать HandleTick с elapsed_ms=10", "Подсчитать вызовы PollSensor"], "expected_result": ["PollSensor() вызван без аргументов ровно 1 раз"]}</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n"/>
+      <c r="N61" s="2" t="n"/>
+      <c r="O61" s="2" t="n"/>
+      <c r="P61" s="2" t="n"/>
+      <c r="Q61" s="2" t="n"/>
+      <c r="R61" s="2" t="n"/>
+      <c r="S61" s="2" t="n"/>
+      <c r="T61" s="2" t="n"/>
+      <c r="U61" s="2" t="n"/>
+      <c r="V61" s="2" t="n"/>
+      <c r="W61" s="2" t="n"/>
+      <c r="X61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004::E001</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>TC_TIME_11</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_TIME_11 обеспечивает положительное покрытие элемента DEMO_TIME_004::E001. Входы теста (elapsed_ms=11) удовлетворяют условию применимости (&gt;= 10). Действие вызова HandleTick присутствует в шагах, а ожидаемый результат (ровно один вызов PollSensor) подтверждается expected_result и фактически наблюдается после подсчета вызовов.
+Точные совпадения: HandleTick, PollSensor, elapsed_ms
+Отсутствующие токены: 10
+Цитаты теста: {"preconditions": ["Журнал PollSensor очищен"], "steps": ["Вызвать HandleTick с elapsed_ms=11", "Подсчитать вызовы PollSensor"], "expected_result": ["PollSensor() вызван без аргументов ровно 1 раз"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 10</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F62" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="n"/>
+      <c r="M62" s="2" t="n"/>
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="n"/>
+      <c r="P62" s="2" t="n"/>
+      <c r="Q62" s="2" t="n"/>
+      <c r="R62" s="2" t="n"/>
+      <c r="S62" s="2" t="n"/>
+      <c r="T62" s="2" t="n"/>
+      <c r="U62" s="2" t="n"/>
+      <c r="V62" s="2" t="n"/>
+      <c r="W62" s="2" t="n"/>
+      <c r="X62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004::E002</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>TC_TIME_9</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_TIME_9 полностью покрывает элемент DEMO_TIME_004::E002. Входное условие 'elapsed_ms=9' соответствует требованию 'меньше 10'. Действие теста 'Вызвать HandleTick с elapsed_ms=9' инициирует проверку. Ожидаемый результат 'PollSensor не вызван' прямо подтверждает обязательство элемента. Все условия применимости истинны.
+Точные совпадения: HandleTick, PollSensor, elapsed_ms
+Отсутствующие токены: 10
+Цитаты теста: {"preconditions": ["Журнал PollSensor очищен"], "steps": ["Вызвать HandleTick с elapsed_ms=9", "Подсчитать вызовы PollSensor"], "expected_result": ["PollSensor не вызван"]}
+Проверка непротиворечивости: В действиях, входах и результате отсутствуют точные токены: 10</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
+      <c r="P63" s="2" t="n"/>
+      <c r="Q63" s="2" t="n"/>
+      <c r="R63" s="2" t="n"/>
+      <c r="S63" s="2" t="n"/>
+      <c r="T63" s="2" t="n"/>
+      <c r="U63" s="2" t="n"/>
+      <c r="V63" s="2" t="n"/>
+      <c r="W63" s="2" t="n"/>
+      <c r="X63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004::E002</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>TC_TIME_10</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Элемент DEMO_TIME_004::E002 требует отсутствия вызова PollSensor() при условии elapsed_ms &lt; 10. Тест TC_TIME_10 проверяет случай elapsed_ms = 10, который не соответствует условию применимости (меньше 10). Следовательно, тест не покрывает данный элемент.
+Точные совпадения: 10, HandleTick, PollSensor, elapsed_ms
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["Журнал PollSensor очищен"], "steps": ["Вызвать HandleTick с elapsed_ms=10", "Подсчитать вызовы PollSensor"], "expected_result": ["PollSensor() вызван без аргументов ровно 1 раз"]}</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F64" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="n"/>
+      <c r="Q64" s="2" t="n"/>
+      <c r="R64" s="2" t="n"/>
+      <c r="S64" s="2" t="n"/>
+      <c r="T64" s="2" t="n"/>
+      <c r="U64" s="2" t="n"/>
+      <c r="V64" s="2" t="n"/>
+      <c r="W64" s="2" t="n"/>
+      <c r="X64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_TIME_004::E002</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>TC_TIME_11</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_TIME_11 проверяет ветвь требования DEMO_TIME_004::E002 (не вызывать PollSensor), когда elapsed_ms &gt;= 10. Входное значение elapsed_ms=11 не соответствует условию применимости элемента (elapsed_ms &lt; 10). Следовательно, тест не может подтвердить отсутствие вызова функции в контексте данного обязательства.
+Точные совпадения: HandleTick, PollSensor, elapsed_ms
+Отсутствующие токены: 10
+Цитаты теста: {"preconditions": ["Журнал PollSensor очищен"], "steps": ["Вызвать HandleTick с elapsed_ms=11", "Подсчитать вызовы PollSensor"], "expected_result": ["PollSensor() вызван без аргументов ровно 1 раз"]}</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="n"/>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="n"/>
+      <c r="P65" s="2" t="n"/>
+      <c r="Q65" s="2" t="n"/>
+      <c r="R65" s="2" t="n"/>
+      <c r="S65" s="2" t="n"/>
+      <c r="T65" s="2" t="n"/>
+      <c r="U65" s="2" t="n"/>
+      <c r="V65" s="2" t="n"/>
+      <c r="W65" s="2" t="n"/>
+      <c r="X65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E001</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_GOOD</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_MASK_GOOD покрывает элемент DEMO_MASK_005::E001. Предусловие устанавливает вход old_flags=0xA5 (соответствует условию 'При вызове метода UpdateFlags'). Действие 'Вызвать UpdateFlags' активирует логику вычисления. Ожидаемый результат содержит конкретное значение new_flags=0xAC, полученное по формуле из требования ((0xA5 &amp; ~0x0F) | (0x3C &amp; 0x0F) = 0x80 | 0x3C = 0xBC? Нет, 0xA5 &amp; 0xF0 = 0xA0. 0xA0 | 0x3C = 0xBC. В тесте указано 0xAC. Это противоречие). Пересчитаем: old=0xA5 (1010 0101), mask ~0x0F = ...1110 0000. old &amp; ~0x0F = 1010 0000 (0xA0). requested=0x3C (0011 1100). requested &amp; 0x0F = 0000 1100 (0x0C). Результат: 0xA0 | 0x0C = 0xAC. Вычисления верны. Тест проверяет действие вычисления и конкретный результат, подтверждая выполнение формулы для данного входа.
+Точные совпадения: 0x0F, UpdateFlags, new_flags, old_flags, requested_flags
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["old_flags = 0xA5"], "steps": ["Вызвать UpdateFlags"], "expected_result": ["new_flags = 0xAC; биты вне 0x0F сохранены от old_flags, биты внутри 0x0F взяты из requested_flags"]}</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
+      <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="n"/>
+      <c r="Q66" s="2" t="n"/>
+      <c r="R66" s="2" t="n"/>
+      <c r="S66" s="2" t="n"/>
+      <c r="T66" s="2" t="n"/>
+      <c r="U66" s="2" t="n"/>
+      <c r="V66" s="2" t="n"/>
+      <c r="W66" s="2" t="n"/>
+      <c r="X66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E001</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_PARTIAL</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Тест покрывает условие вызова метода UpdateFlags (применимость true). Тест проверяет корректность вычисления младших битов (внутри маски 0x0F), что соответствует элементу E003. Однако тест НЕ проверяет сохранение старших битов (элемент E002), так как в шагах указано 'Проверить только new_flags &amp; 0x0F'. Следовательно, элемент E001 (общая формула) и элемент E002 частично не покрыты этим конкретным аспектом проверки. Покрытие элемента E003 подтверждается ожиданием результата для младшей маски.
+Точные совпадения: 0x0F, UpdateFlags, new_flags, old_flags, requested_flags
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["old_flags = 0xA5"], "steps": ["Вызвать UpdateFlags", "Проверить только new_flags &amp; 0x0F"], "expected_result": ["new_flags &amp; 0x0F = 0x0C"]}</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F67" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="n"/>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="n"/>
+      <c r="P67" s="2" t="n"/>
+      <c r="Q67" s="2" t="n"/>
+      <c r="R67" s="2" t="n"/>
+      <c r="S67" s="2" t="n"/>
+      <c r="T67" s="2" t="n"/>
+      <c r="U67" s="2" t="n"/>
+      <c r="V67" s="2" t="n"/>
+      <c r="W67" s="2" t="n"/>
+      <c r="X67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E001</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Тест устанавливает входное условие (old_flags = 0xA5), которое соответствует условию применимости вызова метода UpdateFlags. Однако тест не содержит конкретных шагов выполнения вычисления формулы или проверки конкретного числового результата, удовлетворяющего логике ветвления 'биты вне маски' и 'биты внутри маски'. Упоминание проверки битов в шагах слишком абстрактно для доказательства покрытия конкретной арифметической логики элемента.
+Точные совпадения: 0x0F, UpdateFlags, new_flags, old_flags, requested_flags
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["old_flags = 0xA5"], "steps": ["Проверить new_flags и отдельно старшие/младшие биты"], "expected_result": []}</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="n"/>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="n"/>
+      <c r="P68" s="2" t="n"/>
+      <c r="Q68" s="2" t="n"/>
+      <c r="R68" s="2" t="n"/>
+      <c r="S68" s="2" t="n"/>
+      <c r="T68" s="2" t="n"/>
+      <c r="U68" s="2" t="n"/>
+      <c r="V68" s="2" t="n"/>
+      <c r="W68" s="2" t="n"/>
+      <c r="X68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E002</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_GOOD</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_MASK_GOOD удовлетворяет условию применимости (вызов UpdateFlags с old_flags=0xA5). В expected_result явно указано ожидаемое поведение для бит вне маски: 'биты вне 0x0F сохранены от old_flags'. Однако в steps действие проверки описано слишком абстрактно ('Проверить new_flags и отдельно старшие/младшие биты') без указания конкретного действия, которое доказывает сохранение значений (например, сравнение конкретных бит или логическая операция), что делает формальное доказательство покрытия по цитатам действий неполным.
+Точные совпадения: 0x0F, UpdateFlags, new_flags, old_flags
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["old_flags = 0xA5"], "steps": ["Проверить new_flags и отдельно старшие/младшие биты"], "expected_result": ["new_flags = 0xAC; биты вне 0x0F сохранены от old_flags, биты внутри 0x0F взяты из requested_flags"]}</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F69" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n"/>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="n"/>
+      <c r="P69" s="2" t="n"/>
+      <c r="Q69" s="2" t="n"/>
+      <c r="R69" s="2" t="n"/>
+      <c r="S69" s="2" t="n"/>
+      <c r="T69" s="2" t="n"/>
+      <c r="U69" s="2" t="n"/>
+      <c r="V69" s="2" t="n"/>
+      <c r="W69" s="2" t="n"/>
+      <c r="X69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E002</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_PARTIAL</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>не покрыт</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Элемент требует проверки сохранения бит вне маски 0x0F (верхние биты) в new_flags. Тест проверяет только младшие биты (new_flags &amp; 0x0F). Входные данные old_flags = 0xA5 содержат информацию о верхних битах, но шаг теста явно исключает их проверку ('Проверить только new_flags &amp; 0x0F'). Ожидаемый результат подтверждает корректность только нижней части маски. Следовательно, поведение элемента относительно сохранения верхних битов не было протестировано.
+Точные совпадения: 0x0F, UpdateFlags, new_flags, old_flags
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["old_flags = 0xA5"], "steps": ["Проверить только new_flags &amp; 0x0F"], "expected_result": ["new_flags &amp; 0x0F = 0x0C"]}</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F70" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="2" t="n"/>
+      <c r="N70" s="2" t="n"/>
+      <c r="O70" s="2" t="n"/>
+      <c r="P70" s="2" t="n"/>
+      <c r="Q70" s="2" t="n"/>
+      <c r="R70" s="2" t="n"/>
+      <c r="S70" s="2" t="n"/>
+      <c r="T70" s="2" t="n"/>
+      <c r="U70" s="2" t="n"/>
+      <c r="V70" s="2" t="n"/>
+      <c r="W70" s="2" t="n"/>
+      <c r="X70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E002</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Тест содержит входные данные (old_flags=0xA5, requested_flags=0x3C) и шаги проверки, однако в поле expected_result нет точной непрерывной цитаты из требования, подтверждающей сохранение бит вне маски для конкретно этого элемента. Фраза 'биты вне 0x0F сохранены от old_flags' является пересказом логики, а не прямой цитатой условия соответствия, требуемой по инструкции ('Для покрыт приведи точные непрерывные цитаты из steps и expected_result... Нет доказательства — не покрыт или требует проверки'). Также отсутствует явное утверждение в ожидаемом результате о том, что результат равен 0xAC (хотя это вычисляется), что делает доказательство покрытия конкретного элемента E002 неполным согласно строгим правилам цитирования.
+Точные совпадения: 0x0F, UpdateFlags, new_flags, old_flags
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["old_flags = 0xA5"], "steps": ["Проверить new_flags и отдельно старшие/младшие биты"], "expected_result": ["биты вне 0x0F сохранены от old_flags"]}</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F71" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="n"/>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n"/>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="n"/>
+      <c r="P71" s="2" t="n"/>
+      <c r="Q71" s="2" t="n"/>
+      <c r="R71" s="2" t="n"/>
+      <c r="S71" s="2" t="n"/>
+      <c r="T71" s="2" t="n"/>
+      <c r="U71" s="2" t="n"/>
+      <c r="V71" s="2" t="n"/>
+      <c r="W71" s="2" t="n"/>
+      <c r="X71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E003</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_GOOD</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Тест проверяет обновление младших битов (маска 0x0F). Входные данные old_flags=0xA5 и requested_flags=0x3C соответствуют условию вызова UpdateFlags. Однако в шагах теста отсутствует явное указание на передачу конкретных значений параметров в функцию или проверку конкретных битовых позиций внутри маски, что делает доказательство выполнения именно элемента E003 (принятие значений из requested_flags) косвенным.
+Точные совпадения: 0x0F, UpdateFlags, new_flags, requested_flags
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["old_flags = 0xA5"], "steps": ["Проверить new_flags и отдельно старшие/младшие биты"], "expected_result": ["new_flags = 0xAC; биты вне 0x0F сохранены от old_flags, биты внутри 0x0F взяты из requested_flags"]}</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F72" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n"/>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="n"/>
+      <c r="P72" s="2" t="n"/>
+      <c r="Q72" s="2" t="n"/>
+      <c r="R72" s="2" t="n"/>
+      <c r="S72" s="2" t="n"/>
+      <c r="T72" s="2" t="n"/>
+      <c r="U72" s="2" t="n"/>
+      <c r="V72" s="2" t="n"/>
+      <c r="W72" s="2" t="n"/>
+      <c r="X72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E003</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_PARTIAL</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>покрыт</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Тест TC_MASK_PARTIAL при вызове UpdateFlags с old_flags=0xA5 и requested_flags=0x3C выполняет проверку выражения new_flags &amp; 0x0F == 0x0C. Это доказывает, что биты внутри маски (младшие 4 бита) были обновлены до значений из requested_flags (0x3C &amp; 0x0F = 0x0C), что соответствует требованию элемента E003.
+Точные совпадения: 0x0F, UpdateFlags, new_flags, requested_flags
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["old_flags = 0xA5"], "steps": ["Проверить только new_flags &amp; 0x0F"], "expected_result": ["new_flags &amp; 0x0F = 0x0C"]}</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F73" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="2" t="n"/>
+      <c r="N73" s="2" t="n"/>
+      <c r="O73" s="2" t="n"/>
+      <c r="P73" s="2" t="n"/>
+      <c r="Q73" s="2" t="n"/>
+      <c r="R73" s="2" t="n"/>
+      <c r="S73" s="2" t="n"/>
+      <c r="T73" s="2" t="n"/>
+      <c r="U73" s="2" t="n"/>
+      <c r="V73" s="2" t="n"/>
+      <c r="W73" s="2" t="n"/>
+      <c r="X73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MASK_005::E003</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>TC_MASK_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Тест не содержит доказательств выполнения требования для конкретного элемента (биты внутри маски). В шагах теста ('Проверить new_flags и отдельно старшие/младшие биты') отсутствует описание реальных действий по извлечению бит или логическому сравнению значений. В ожидаемом результате указано, что 'биты внутри 0x0F взяты из requested_flags', но это является констатацией факта совпадения с формулой общего требования (E001), а не доказательством проверки именно аспекта E003 (что биты внутри маски действительно были перезаписаны значениями из requested_flags и не сохранили старых значений). Нет цитаты, описывающей действие 'сравнить младшие 4 бита new_flags с младшими 4 битами requested_flags'.
+Точные совпадения: 0x0F, UpdateFlags, new_flags, requested_flags
+Отсутствующие токены: нет
+Цитаты теста: {"preconditions": ["old_flags = 0xA5"], "steps": [], "expected_result": ["new_flags = 0xAC; биты вне 0x0F сохранены от old_flags, биты внутри 0x0F взяты из requested_flags"]}</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>ожидает проверки</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="n"/>
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="n"/>
+      <c r="M74" s="2" t="n"/>
+      <c r="N74" s="2" t="n"/>
+      <c r="O74" s="2" t="n"/>
+      <c r="P74" s="2" t="n"/>
+      <c r="Q74" s="2" t="n"/>
+      <c r="R74" s="2" t="n"/>
+      <c r="S74" s="2" t="n"/>
+      <c r="T74" s="2" t="n"/>
+      <c r="U74" s="2" t="n"/>
+      <c r="V74" s="2" t="n"/>
+      <c r="W74" s="2" t="n"/>
+      <c r="X74" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2339,7 +7701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2393,17 +7755,19 @@
           <t>не зафиксировано</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>не определено</t>
+        </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2417,96 +7781,154 @@
           <t>не зафиксировано</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>не определено</t>
+        </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DEMO_MODE_002</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>не зафиксировано</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>не определено</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>DEMO_LOOP_003</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Новый проект</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+          <t>не зафиксировано</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>не определено</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Исходное покрытие зафиксировано</t>
+          <t>DEMO_TIME_004</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Нет: исторический процент не восстанавливается из текущих связей</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+          <t>не зафиксировано</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>не определено</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Сгенерированных тестов всего</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
+          <t>DEMO_MASK_005</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>не зафиксировано</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>не определено</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="F7" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Принятых сгенерированных тестов</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
+          <t>DEMO_AMBIG_006</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>не зафиксировано</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>не определено</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Ожидающих проверки сгенерированных тестов</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
@@ -2515,11 +7937,13 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Отклонённых сгенерированных тестов</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>0</v>
+          <t>Проект</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Новый проект</t>
+        </is>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
@@ -2529,11 +7953,13 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Отклонённых элементов (исключены)</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+          <t>Исходное покрытие зафиксировано</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Нет: исторический процент не восстанавливается из текущих связей</t>
+        </is>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
@@ -2543,13 +7969,11 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Замечания анализа требований</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>{"DEMO_RANGE_001": []}</t>
-        </is>
+          <t>Сгенерированных тестов всего</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
@@ -2559,13 +7983,11 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Оценка</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Подтверждённое покрытие активных выделенных элементов; не результат выполнения тестов</t>
-        </is>
+          <t>Принятых сгенерированных тестов</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
@@ -2575,21 +7997,125 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Правило TestCases</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Неотклонённые существующие и только принятые сгенерированные тесты</t>
-        </is>
+          <t>Ожидающих проверки сгенерированных тестов</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Отклонённых сгенерированных тестов</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Отклонённых элементов (исключены)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Элементов с неподтверждённой цитатой (исключены)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Замечания анализа требований</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>{"DEMO_RANGE_001": ["Смысл, условия и полнота требуют ручной проверки. Перефразирование не считается ошибкой"], "DEMO_MODE_002": ["Поведение в режиме ACTIVE при ADC_READY, отличном от 1, не определено.", "Смысл, условия и полнота требуют ручной проверки. Перефразирование не считается ошибкой"], "DEMO_LOOP_003": ["Смысл, условия и полнота требуют ручной проверки. Перефразирование не считается ошибкой"], "DEMO_TIME_004": ["Смысл, условия и полнота требуют ручной проверки. Перефразирование не считается ошибкой"], "DEMO_MASK_005": ["Смысл, условия и полнота требуют ручной проверки. Перефразирование не считается ошибкой"], "DEMO_AMBIG_006": ["ProcessCommand должен быстро обрабатывать команды", "ProcessCommand должен корректно реагировать на некорректные входные данные", "Список команд не указан", "Критерии корректности не указаны", "Допустимое время обработки не указано", "Ожидаемые ответы на команды не указаны", "Модель не выделила обязательств; проверьте достаточность требования", "Смысл, условия и полнота требуют ручной проверки. Перефразирование не считается ошибкой"]}</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Полнота не подтверждена для требований</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>["DEMO_RANGE_001", "DEMO_MODE_002", "DEMO_LOOP_003", "DEMO_TIME_004", "DEMO_MASK_005", "DEMO_AMBIG_006"]</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Оценка</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждённое покрытие активных выделенных элементов; не результат выполнения тестов</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Правило TestCases</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Неотклонённые существующие и только принятые сгенерированные тесты</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
